--- a/upload/itens.xlsx
+++ b/upload/itens.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N729"/>
+  <dimension ref="A1:N728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28081,7 +28081,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>CSS CONSTRUTORA LTDA</t>
+          <t>CSS CONSTRUTORA S.A.</t>
         </is>
       </c>
       <c r="F495" t="n">
@@ -32883,17 +32883,17 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>9422060</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>DM-008/2024</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -32919,13 +32919,13 @@
         <v>1</v>
       </c>
       <c r="L581" t="n">
-        <v>59075097</v>
+        <v>45388427.46</v>
       </c>
       <c r="M581" t="n">
-        <v>59075097</v>
+        <v>45388427.46</v>
       </c>
       <c r="N581" t="n">
-        <v>41801980.63</v>
+        <v>31307061.77</v>
       </c>
     </row>
     <row r="582">
@@ -32944,7 +32944,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>DM-008/2024</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -32995,17 +32995,17 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DM-009/2024</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
         </is>
       </c>
       <c r="F583" t="n">
@@ -33031,13 +33031,13 @@
         <v>1</v>
       </c>
       <c r="L583" t="n">
-        <v>45388427.46</v>
+        <v>49516428.28</v>
       </c>
       <c r="M583" t="n">
-        <v>45388427.46</v>
+        <v>49516428.28</v>
       </c>
       <c r="N583" t="n">
-        <v>31307061.77</v>
+        <v>30648355.12</v>
       </c>
     </row>
     <row r="584">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>DM-009/2024</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -33112,7 +33112,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-025/2023-A</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -33163,17 +33163,17 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>DM-025/2023-A</t>
+          <t>DM-012/2024</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
+          <t>CONSTRUTORA ZAG LTDA</t>
         </is>
       </c>
       <c r="F586" t="n">
@@ -33199,13 +33199,13 @@
         <v>1</v>
       </c>
       <c r="L586" t="n">
-        <v>49516428.28</v>
+        <v>42427903.76</v>
       </c>
       <c r="M586" t="n">
-        <v>49516428.28</v>
+        <v>42427903.76</v>
       </c>
       <c r="N586" t="n">
-        <v>30648355.12</v>
+        <v>29715772.52</v>
       </c>
     </row>
     <row r="587">
@@ -33224,7 +33224,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>DM-012/2024</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -33270,22 +33270,22 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000039/2023</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9410180</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DM-032/2023</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ZAG LTDA</t>
+          <t>CROS CONSTRUCOES S/A</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -33311,13 +33311,13 @@
         <v>1</v>
       </c>
       <c r="L588" t="n">
-        <v>42427903.76</v>
+        <v>51900209.21</v>
       </c>
       <c r="M588" t="n">
-        <v>42427903.76</v>
+        <v>51900209.21</v>
       </c>
       <c r="N588" t="n">
-        <v>29715772.52</v>
+        <v>43983527.2</v>
       </c>
     </row>
     <row r="589">
@@ -33326,22 +33326,22 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>2301762 000039/2023</t>
+          <t>2301762 000041/2023</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>9410180</t>
+          <t>9410175</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>DM-032/2023</t>
+          <t>DM-031/2023</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>CROS CONSTRUCOES S/A</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -33367,13 +33367,13 @@
         <v>1</v>
       </c>
       <c r="L589" t="n">
-        <v>51900209.21</v>
+        <v>17443062.11</v>
       </c>
       <c r="M589" t="n">
-        <v>51900209.21</v>
+        <v>17443062.11</v>
       </c>
       <c r="N589" t="n">
-        <v>43983527.2</v>
+        <v>16521453.91</v>
       </c>
     </row>
     <row r="590">
@@ -33382,22 +33382,22 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>2301762 000041/2023</t>
+          <t>2301762 000045/2023</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>9410175</t>
+          <t>9424377</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>DM-031/2023</t>
+          <t>DM-019/2024</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>SINALMIG SINAIS E SISTEMAS LTDA</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -33420,16 +33420,16 @@
         </is>
       </c>
       <c r="K590" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L590" t="n">
-        <v>17443062.11</v>
+        <v>11996710.85</v>
       </c>
       <c r="M590" t="n">
-        <v>17443062.11</v>
+        <v>11996710.85</v>
       </c>
       <c r="N590" t="n">
-        <v>16521453.91</v>
+        <v>8049000</v>
       </c>
     </row>
     <row r="591">
@@ -33438,22 +33438,22 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>2301762 000045/2023</t>
+          <t>2301762 000046/2023</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>9424377</t>
+          <t>9413969</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>DM-019/2024</t>
+          <t>DM-004/2024</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>SINALMIG SINAIS E SISTEMAS LTDA</t>
+          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -33476,16 +33476,16 @@
         </is>
       </c>
       <c r="K591" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L591" t="n">
-        <v>11996710.85</v>
+        <v>1009319.98</v>
       </c>
       <c r="M591" t="n">
-        <v>11996710.85</v>
+        <v>1009319.98</v>
       </c>
       <c r="N591" t="n">
-        <v>8049000</v>
+        <v>948728.78</v>
       </c>
     </row>
     <row r="592">
@@ -33494,22 +33494,22 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>2301762 000046/2023</t>
+          <t>2301762 000048/2023</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>9413969</t>
+          <t>9412570</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>DM-004/2024</t>
+          <t>DM-003/2024</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -33535,13 +33535,13 @@
         <v>1</v>
       </c>
       <c r="L592" t="n">
-        <v>1009319.98</v>
+        <v>50023008.61</v>
       </c>
       <c r="M592" t="n">
-        <v>1009319.98</v>
+        <v>50023008.61</v>
       </c>
       <c r="N592" t="n">
-        <v>948728.78</v>
+        <v>46770710.65</v>
       </c>
     </row>
     <row r="593">
@@ -33550,22 +33550,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>2301762 000048/2023</t>
+          <t>2301762 000049/2023</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>9412570</t>
+          <t>9423384</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>DM-003/2024</t>
+          <t>DM-013/2024</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F593" t="n">
@@ -33591,13 +33591,13 @@
         <v>1</v>
       </c>
       <c r="L593" t="n">
-        <v>50023008.61</v>
+        <v>78231455.95999999</v>
       </c>
       <c r="M593" t="n">
-        <v>50023008.61</v>
+        <v>78231455.95999999</v>
       </c>
       <c r="N593" t="n">
-        <v>46770710.65</v>
+        <v>67381496.97</v>
       </c>
     </row>
     <row r="594">
@@ -33606,22 +33606,22 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>2301762 000049/2023</t>
+          <t>2301762 000050/2023</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>9423384</t>
+          <t>9414641</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>DM-013/2024</t>
+          <t>DM-006/2024</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>E. B. O. - EMPRESA BRASILEIRA DE OBRAS LTDA</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -33647,13 +33647,13 @@
         <v>1</v>
       </c>
       <c r="L594" t="n">
-        <v>78231455.95999999</v>
+        <v>7567396.72</v>
       </c>
       <c r="M594" t="n">
-        <v>78231455.95999999</v>
+        <v>7567396.72</v>
       </c>
       <c r="N594" t="n">
-        <v>67381496.97</v>
+        <v>5949066.1</v>
       </c>
     </row>
     <row r="595">
@@ -33662,22 +33662,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>2301762 000050/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>9414641</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>DM-006/2024</t>
+          <t>DM-014/2024</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>E. B. O. - EMPRESA BRASILEIRA DE OBRAS LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F595" t="n">
@@ -33703,13 +33703,13 @@
         <v>1</v>
       </c>
       <c r="L595" t="n">
-        <v>7567396.72</v>
+        <v>57753580.93</v>
       </c>
       <c r="M595" t="n">
-        <v>7567396.72</v>
+        <v>57753580.93</v>
       </c>
       <c r="N595" t="n">
-        <v>5949066.1</v>
+        <v>37310856.76</v>
       </c>
     </row>
     <row r="596">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>DM-014/2024</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -33779,17 +33779,17 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-018/2024</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="F597" t="n">
@@ -33815,13 +33815,13 @@
         <v>1</v>
       </c>
       <c r="L597" t="n">
-        <v>57753580.93</v>
+        <v>56623238.81</v>
       </c>
       <c r="M597" t="n">
-        <v>57753580.93</v>
+        <v>56623238.81</v>
       </c>
       <c r="N597" t="n">
-        <v>37310856.76</v>
+        <v>37153801.63</v>
       </c>
     </row>
     <row r="598">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>DM-018/2024</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -33891,17 +33891,17 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DM-016/2024</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -33927,13 +33927,13 @@
         <v>1</v>
       </c>
       <c r="L599" t="n">
-        <v>56623238.81</v>
+        <v>51505163.41</v>
       </c>
       <c r="M599" t="n">
-        <v>56623238.81</v>
+        <v>51505163.41</v>
       </c>
       <c r="N599" t="n">
-        <v>37153801.63</v>
+        <v>33479427.94</v>
       </c>
     </row>
     <row r="600">
@@ -33952,7 +33952,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>DM-016/2024</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -34003,17 +34003,17 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9424447</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-015/2024</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -34039,13 +34039,13 @@
         <v>1</v>
       </c>
       <c r="L601" t="n">
-        <v>51505163.41</v>
+        <v>50334501.36</v>
       </c>
       <c r="M601" t="n">
-        <v>51505163.41</v>
+        <v>50334501.36</v>
       </c>
       <c r="N601" t="n">
-        <v>33479427.94</v>
+        <v>33230906.95</v>
       </c>
     </row>
     <row r="602">
@@ -34059,17 +34059,17 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>9424447</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>DM-015/2024</t>
+          <t>DM-017/2024</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -34095,13 +34095,13 @@
         <v>1</v>
       </c>
       <c r="L602" t="n">
-        <v>50334501.36</v>
+        <v>50026623.29</v>
       </c>
       <c r="M602" t="n">
-        <v>50334501.36</v>
+        <v>50026623.29</v>
       </c>
       <c r="N602" t="n">
-        <v>33230906.95</v>
+        <v>32023158.45</v>
       </c>
     </row>
     <row r="603">
@@ -34120,7 +34120,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>DM-017/2024</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -34171,17 +34171,17 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DM-020/2024</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -34207,13 +34207,13 @@
         <v>1</v>
       </c>
       <c r="L604" t="n">
-        <v>50026623.29</v>
+        <v>57899353.16</v>
       </c>
       <c r="M604" t="n">
-        <v>50026623.29</v>
+        <v>57899353.16</v>
       </c>
       <c r="N604" t="n">
-        <v>32023158.45</v>
+        <v>34984519.25</v>
       </c>
     </row>
     <row r="605">
@@ -34232,7 +34232,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>DM-020/2024</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -34283,17 +34283,17 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-022/2024</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F606" t="n">
@@ -34319,13 +34319,13 @@
         <v>1</v>
       </c>
       <c r="L606" t="n">
-        <v>57899353.16</v>
+        <v>61509573.94</v>
       </c>
       <c r="M606" t="n">
-        <v>57899353.16</v>
+        <v>61509573.94</v>
       </c>
       <c r="N606" t="n">
-        <v>34984519.25</v>
+        <v>42788655.89</v>
       </c>
     </row>
     <row r="607">
@@ -34344,7 +34344,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>DM-022/2024</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -34390,54 +34390,54 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301931 000001/2024</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9440673</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>AEST-009440673/2024</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F608" t="n">
         <v>1</v>
       </c>
       <c r="G608" t="n">
-        <v>1872</v>
+        <v>26883</v>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I608" t="n">
-        <v>5107</v>
+        <v>3502</v>
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K608" t="n">
         <v>1</v>
       </c>
       <c r="L608" t="n">
-        <v>61509573.94</v>
+        <v>7699669.8</v>
       </c>
       <c r="M608" t="n">
-        <v>61509573.94</v>
+        <v>7699669.8</v>
       </c>
       <c r="N608" t="n">
-        <v>42788655.89</v>
+        <v>5774752.44</v>
       </c>
     </row>
     <row r="609">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>AEST-009440673/2024</t>
+          <t>PO</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -34502,22 +34502,22 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>2301931 000001/2024</t>
+          <t>2301931 000002/2024</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>9440673</t>
+          <t>9441233</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>AEST-9441233/2024</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA E EXTENSAO UNIVERSITARIA</t>
         </is>
       </c>
       <c r="F610" t="n">
@@ -34543,13 +34543,13 @@
         <v>1</v>
       </c>
       <c r="L610" t="n">
-        <v>7699669.8</v>
+        <v>5947278.86</v>
       </c>
       <c r="M610" t="n">
-        <v>7699669.8</v>
+        <v>0</v>
       </c>
       <c r="N610" t="n">
-        <v>5774752.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="611">
@@ -34588,11 +34588,11 @@
         </is>
       </c>
       <c r="I611" t="n">
-        <v>3502</v>
+        <v>3973</v>
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
         </is>
       </c>
       <c r="K611" t="n">
@@ -34602,66 +34602,66 @@
         <v>5947278.86</v>
       </c>
       <c r="M611" t="n">
-        <v>0</v>
+        <v>5947278.86</v>
       </c>
       <c r="N611" t="n">
-        <v>0</v>
+        <v>5947278.86</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>2301931 000002/2024</t>
+          <t>1301017 000043/2024</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>9441233</t>
+          <t>9473911</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>AEST-9441233/2024</t>
+          <t>9473911/2024</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA E EXTENSAO UNIVERSITARIA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="F612" t="n">
         <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>26883</v>
+        <v>11207</v>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I612" t="n">
-        <v>3973</v>
+        <v>3951</v>
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K612" t="n">
         <v>1</v>
       </c>
       <c r="L612" t="n">
-        <v>5947278.86</v>
+        <v>6941645.22</v>
       </c>
       <c r="M612" t="n">
-        <v>5947278.86</v>
+        <v>6941645.22</v>
       </c>
       <c r="N612" t="n">
-        <v>5947278.86</v>
+        <v>5206233.96</v>
       </c>
     </row>
     <row r="613">
@@ -34689,7 +34689,7 @@
         </is>
       </c>
       <c r="F613" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G613" t="n">
         <v>11207</v>
@@ -34714,10 +34714,10 @@
         <v>6941645.22</v>
       </c>
       <c r="M613" t="n">
-        <v>6941645.22</v>
+        <v>0</v>
       </c>
       <c r="N613" t="n">
-        <v>5206233.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
@@ -34745,7 +34745,7 @@
         </is>
       </c>
       <c r="F614" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G614" t="n">
         <v>11207</v>
@@ -34782,54 +34782,54 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>1301017 000043/2024</t>
+          <t>1301606 000001/2025</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>9473911</t>
+          <t>9470224</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>9473911/2024</t>
+          <t>DC-9470224/2025</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>SENGE SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F615" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I615" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K615" t="n">
         <v>1</v>
       </c>
       <c r="L615" t="n">
-        <v>6941645.22</v>
+        <v>25933131.61</v>
       </c>
       <c r="M615" t="n">
-        <v>0</v>
+        <v>25933131.61</v>
       </c>
       <c r="N615" t="n">
-        <v>0</v>
+        <v>19446841.31</v>
       </c>
     </row>
     <row r="616">
@@ -34838,22 +34838,22 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>1301606 000001/2025</t>
+          <t>2301520 000001/2025</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>9470224</t>
+          <t>9459022</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>DC-9470224/2025</t>
+          <t>DC-9459022/2025</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>SENGE SERVICOS DE ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F616" t="n">
@@ -34879,13 +34879,13 @@
         <v>1</v>
       </c>
       <c r="L616" t="n">
-        <v>25933131.61</v>
+        <v>13090078.19</v>
       </c>
       <c r="M616" t="n">
-        <v>25933131.61</v>
+        <v>13090078.19</v>
       </c>
       <c r="N616" t="n">
-        <v>19446841.31</v>
+        <v>9817558.640000001</v>
       </c>
     </row>
     <row r="617">
@@ -34899,12 +34899,12 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>9459022</t>
+          <t>9459023</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>DC-9459022/2025</t>
+          <t>DC-9459023/2025</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -34935,13 +34935,13 @@
         <v>1</v>
       </c>
       <c r="L617" t="n">
-        <v>13090078.19</v>
+        <v>39434905.89</v>
       </c>
       <c r="M617" t="n">
-        <v>13090078.19</v>
+        <v>39434905.89</v>
       </c>
       <c r="N617" t="n">
-        <v>9817558.640000001</v>
+        <v>29576179.41</v>
       </c>
     </row>
     <row r="618">
@@ -34950,54 +34950,54 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2301520 000001/2025</t>
+          <t>2301520 000002/2025</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>9459023</t>
+          <t>9472756</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>DC-9459023/2025</t>
+          <t>DC-9472756/2025</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>ESTEL ENGENHARIA LTDA.</t>
         </is>
       </c>
       <c r="F618" t="n">
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I618" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K618" t="n">
         <v>1</v>
       </c>
       <c r="L618" t="n">
-        <v>39434905.89</v>
+        <v>2332947.34</v>
       </c>
       <c r="M618" t="n">
-        <v>39434905.89</v>
+        <v>2332947.34</v>
       </c>
       <c r="N618" t="n">
-        <v>29576179.41</v>
+        <v>1655673.22</v>
       </c>
     </row>
     <row r="619">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>DC-9472756/2025</t>
+          <t>DM-001/2022</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -35062,54 +35062,54 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>2301520 000002/2025</t>
+          <t>2301520 000004/2025</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>9472756</t>
+          <t>9459021</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>DM-001/2022</t>
+          <t>DC-9459021/2025</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>ESTEL ENGENHARIA LTDA.</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F620" t="n">
         <v>1</v>
       </c>
       <c r="G620" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I620" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K620" t="n">
         <v>1</v>
       </c>
       <c r="L620" t="n">
-        <v>2332947.34</v>
+        <v>40411563.13</v>
       </c>
       <c r="M620" t="n">
-        <v>2332947.34</v>
+        <v>40411563.13</v>
       </c>
       <c r="N620" t="n">
-        <v>1655673.22</v>
+        <v>35900000</v>
       </c>
     </row>
     <row r="621">
@@ -35118,22 +35118,22 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>2301520 000004/2025</t>
+          <t>2301520 000007/2025</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>9459021</t>
+          <t>9468321</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>DC-9459021/2025</t>
+          <t>DC-9468321/2025</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>G S COSTA CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="F621" t="n">
@@ -35159,13 +35159,13 @@
         <v>1</v>
       </c>
       <c r="L621" t="n">
-        <v>40411563.13</v>
+        <v>2445446.33</v>
       </c>
       <c r="M621" t="n">
-        <v>40411563.13</v>
+        <v>2445446.33</v>
       </c>
       <c r="N621" t="n">
-        <v>35900000</v>
+        <v>2380000</v>
       </c>
     </row>
     <row r="622">
@@ -35174,54 +35174,54 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>2301520 000007/2025</t>
+          <t>2301520 000008/2025</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>9468321</t>
+          <t>9472752</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>DC-9468321/2025</t>
+          <t>DC-9472752/2025</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>G S COSTA CONSTRUTORA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F622" t="n">
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I622" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K622" t="n">
         <v>1</v>
       </c>
       <c r="L622" t="n">
-        <v>2445446.33</v>
+        <v>9357672.390000001</v>
       </c>
       <c r="M622" t="n">
-        <v>2445446.33</v>
+        <v>9357672.390000001</v>
       </c>
       <c r="N622" t="n">
-        <v>2380000</v>
+        <v>7056321.74</v>
       </c>
     </row>
     <row r="623">
@@ -35240,7 +35240,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>DC-9472752/2025</t>
+          <t>DM-001/2021</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -35286,54 +35286,54 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2301520 000008/2025</t>
+          <t>2301520 000010/2025</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>9472752</t>
+          <t>9473951</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>DM-001/2021</t>
+          <t>DC-9473951/2025</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="F624" t="n">
         <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I624" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K624" t="n">
         <v>1</v>
       </c>
       <c r="L624" t="n">
-        <v>9357672.390000001</v>
+        <v>63771944.67</v>
       </c>
       <c r="M624" t="n">
-        <v>9357672.390000001</v>
+        <v>63771944.67</v>
       </c>
       <c r="N624" t="n">
-        <v>7056321.74</v>
+        <v>45918998.95</v>
       </c>
     </row>
     <row r="625">
@@ -35342,22 +35342,22 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>2301520 000010/2025</t>
+          <t>2301520 000011/2025</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>9473951</t>
+          <t>9471605</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>DC-9473951/2025</t>
+          <t>DC-9471605/2025</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="F625" t="n">
@@ -35383,13 +35383,13 @@
         <v>1</v>
       </c>
       <c r="L625" t="n">
-        <v>63771944.67</v>
+        <v>9523161.51</v>
       </c>
       <c r="M625" t="n">
-        <v>63771944.67</v>
+        <v>9523161.51</v>
       </c>
       <c r="N625" t="n">
-        <v>45918998.95</v>
+        <v>9522992.289999999</v>
       </c>
     </row>
     <row r="626">
@@ -35398,22 +35398,22 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2301520 000011/2025</t>
+          <t>2301520 000016/2025</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>9471605</t>
+          <t>9473175</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>DC-9471605/2025</t>
+          <t>DC-009473175/2025</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>CONSTRUTORA A GASPAR S/A</t>
         </is>
       </c>
       <c r="F626" t="n">
@@ -35439,13 +35439,13 @@
         <v>1</v>
       </c>
       <c r="L626" t="n">
-        <v>9523161.51</v>
+        <v>252967153.57</v>
       </c>
       <c r="M626" t="n">
-        <v>9523161.51</v>
+        <v>252967153.57</v>
       </c>
       <c r="N626" t="n">
-        <v>9522992.289999999</v>
+        <v>207490000</v>
       </c>
     </row>
     <row r="627">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>DC-009473175/2025</t>
+          <t>DC-012/2023</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -35510,22 +35510,22 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>2301520 000016/2025</t>
+          <t>2301520 000018/2025</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>9473175</t>
+          <t>9473949</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>DC-012/2023</t>
+          <t>DC-9473949/2025</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>CONSTRUTORA A GASPAR S/A</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="F628" t="n">
@@ -35551,13 +35551,13 @@
         <v>1</v>
       </c>
       <c r="L628" t="n">
-        <v>252967153.57</v>
+        <v>7210196.37</v>
       </c>
       <c r="M628" t="n">
-        <v>252967153.57</v>
+        <v>7210196.37</v>
       </c>
       <c r="N628" t="n">
-        <v>207490000</v>
+        <v>5978999.99</v>
       </c>
     </row>
     <row r="629">
@@ -35566,22 +35566,22 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>2301520 000018/2025</t>
+          <t>2301520 000019/2024</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>9473949</t>
+          <t>9447760</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>DC-9473949/2025</t>
+          <t>DC-9447760/2025</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F629" t="n">
@@ -35607,13 +35607,13 @@
         <v>1</v>
       </c>
       <c r="L629" t="n">
-        <v>7210196.37</v>
+        <v>9049369.99</v>
       </c>
       <c r="M629" t="n">
-        <v>7210196.37</v>
+        <v>9049369.99</v>
       </c>
       <c r="N629" t="n">
-        <v>5978999.99</v>
+        <v>8415499.810000001</v>
       </c>
     </row>
     <row r="630">
@@ -35627,12 +35627,12 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>9447760</t>
+          <t>9447761</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>DC-9447760/2025</t>
+          <t>DC-9447761/2025</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -35663,13 +35663,13 @@
         <v>1</v>
       </c>
       <c r="L630" t="n">
-        <v>9049369.99</v>
+        <v>5032564.85</v>
       </c>
       <c r="M630" t="n">
-        <v>9049369.99</v>
+        <v>5032564.85</v>
       </c>
       <c r="N630" t="n">
-        <v>8415499.810000001</v>
+        <v>4776981.58</v>
       </c>
     </row>
     <row r="631">
@@ -35678,54 +35678,54 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>2301520 000019/2024</t>
+          <t>2301520 000022/2025</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>9447761</t>
+          <t>9492718</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>DC-9447761/2025</t>
+          <t>DC-9492718/2025</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
         </is>
       </c>
       <c r="F631" t="n">
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I631" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K631" t="n">
         <v>1</v>
       </c>
       <c r="L631" t="n">
-        <v>5032564.85</v>
+        <v>4575396.26</v>
       </c>
       <c r="M631" t="n">
-        <v>5032564.85</v>
+        <v>4575396.26</v>
       </c>
       <c r="N631" t="n">
-        <v>4776981.58</v>
+        <v>3187539.16</v>
       </c>
     </row>
     <row r="632">
@@ -35734,17 +35734,17 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>2301520 000022/2025</t>
+          <t>2301520 000023/2025</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>9492718</t>
+          <t>9492065</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>DC-9492718/2025</t>
+          <t>DC-9492065/2025</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -35775,13 +35775,13 @@
         <v>1</v>
       </c>
       <c r="L632" t="n">
-        <v>4575396.26</v>
+        <v>3499878.79</v>
       </c>
       <c r="M632" t="n">
-        <v>4575396.26</v>
+        <v>3499878.79</v>
       </c>
       <c r="N632" t="n">
-        <v>3187539.16</v>
+        <v>2624909.09</v>
       </c>
     </row>
     <row r="633">
@@ -35790,54 +35790,54 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>2301520 000023/2025</t>
+          <t>2301520 000024/2024</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>9492065</t>
+          <t>9458476</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>DC-9492065/2025</t>
+          <t>DC-9458476/2025</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F633" t="n">
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I633" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K633" t="n">
         <v>1</v>
       </c>
       <c r="L633" t="n">
-        <v>3499878.79</v>
+        <v>104863231.67</v>
       </c>
       <c r="M633" t="n">
-        <v>3499878.79</v>
+        <v>104863231.67</v>
       </c>
       <c r="N633" t="n">
-        <v>2624909.09</v>
+        <v>78647423.75</v>
       </c>
     </row>
     <row r="634">
@@ -35846,54 +35846,54 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>2301520 000024/2024</t>
+          <t>2301520 000024/2025</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>9458476</t>
+          <t>9491012</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>DC-9458476/2025</t>
+          <t>DC-9491012/2025</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
         </is>
       </c>
       <c r="F634" t="n">
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I634" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K634" t="n">
         <v>1</v>
       </c>
       <c r="L634" t="n">
-        <v>104863231.67</v>
+        <v>5765714.24</v>
       </c>
       <c r="M634" t="n">
-        <v>104863231.67</v>
+        <v>5765714.24</v>
       </c>
       <c r="N634" t="n">
-        <v>78647423.75</v>
+        <v>4324285.68</v>
       </c>
     </row>
     <row r="635">
@@ -35902,54 +35902,54 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>2301520 000024/2025</t>
+          <t>2301520 000025/2024</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>9491012</t>
+          <t>9448965</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>DC-9491012/2025</t>
+          <t>DC-9448965/2025</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
+          <t>CONSTRUTORA MARINS LTDA</t>
         </is>
       </c>
       <c r="F635" t="n">
         <v>1</v>
       </c>
       <c r="G635" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I635" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K635" t="n">
         <v>1</v>
       </c>
       <c r="L635" t="n">
-        <v>5765714.24</v>
+        <v>4553972.46</v>
       </c>
       <c r="M635" t="n">
-        <v>5765714.24</v>
+        <v>4553972.46</v>
       </c>
       <c r="N635" t="n">
-        <v>4324285.68</v>
+        <v>4553800</v>
       </c>
     </row>
     <row r="636">
@@ -35958,54 +35958,54 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>2301520 000025/2024</t>
+          <t>2301520 000027/2023</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>9448965</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>DC-9448965/2025</t>
+          <t>DC-9453556/2025</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>CONSTRUTORA MARINS LTDA</t>
+          <t>PROJEL - ENGENHARIA ESPECIALIZADA LTDA</t>
         </is>
       </c>
       <c r="F636" t="n">
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I636" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K636" t="n">
         <v>1</v>
       </c>
       <c r="L636" t="n">
-        <v>4553972.46</v>
+        <v>10169679.88</v>
       </c>
       <c r="M636" t="n">
-        <v>4553972.46</v>
+        <v>10169679.88</v>
       </c>
       <c r="N636" t="n">
-        <v>4553800</v>
+        <v>9659997.08</v>
       </c>
     </row>
     <row r="637">
@@ -36024,7 +36024,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>DC-9453556/2025</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -36070,54 +36070,54 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>2301520 000027/2023</t>
+          <t>2301520 000027/2024</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9458861</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9458861/2025</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>PROJEL - ENGENHARIA ESPECIALIZADA LTDA</t>
+          <t>BT CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F638" t="n">
         <v>1</v>
       </c>
       <c r="G638" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I638" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K638" t="n">
         <v>1</v>
       </c>
       <c r="L638" t="n">
-        <v>10169679.88</v>
+        <v>32377230.57</v>
       </c>
       <c r="M638" t="n">
-        <v>10169679.88</v>
+        <v>32377230.57</v>
       </c>
       <c r="N638" t="n">
-        <v>9659997.08</v>
+        <v>24981452.5</v>
       </c>
     </row>
     <row r="639">
@@ -36126,22 +36126,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>2301520 000027/2024</t>
+          <t>2301520 000028/2025</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>9458861</t>
+          <t>9491013</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>DC-9458861/2025</t>
+          <t>DC-9491013/2025</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>BT CONSTRUCOES LTDA</t>
+          <t>VEREDA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F639" t="n">
@@ -36167,13 +36167,13 @@
         <v>1</v>
       </c>
       <c r="L639" t="n">
-        <v>32377230.57</v>
+        <v>22364155.09</v>
       </c>
       <c r="M639" t="n">
-        <v>32377230.57</v>
+        <v>22364155.09</v>
       </c>
       <c r="N639" t="n">
-        <v>24981452.5</v>
+        <v>20125000</v>
       </c>
     </row>
     <row r="640">
@@ -36182,22 +36182,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>2301520 000028/2025</t>
+          <t>2301520 000029/2025</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>9491013</t>
+          <t>9478759</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>DC-9491013/2025</t>
+          <t>DC-9478759/2025</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>VEREDA ENGENHARIA LTDA</t>
+          <t>SOCIEDADE GERAL DE EMPREITADAS LIMITADA -</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -36223,13 +36223,13 @@
         <v>1</v>
       </c>
       <c r="L640" t="n">
-        <v>22364155.09</v>
+        <v>17183580.33</v>
       </c>
       <c r="M640" t="n">
-        <v>22364155.09</v>
+        <v>17183580.33</v>
       </c>
       <c r="N640" t="n">
-        <v>20125000</v>
+        <v>14619000</v>
       </c>
     </row>
     <row r="641">
@@ -36238,54 +36238,54 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>2301520 000029/2025</t>
+          <t>2301520 000031/2025</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>9478759</t>
+          <t>9481581</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>DC-9478759/2025</t>
+          <t>DC-9481581/2025</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>SOCIEDADE GERAL DE EMPREITADAS LIMITADA -</t>
+          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
         </is>
       </c>
       <c r="F641" t="n">
         <v>1</v>
       </c>
       <c r="G641" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I641" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K641" t="n">
         <v>1</v>
       </c>
       <c r="L641" t="n">
-        <v>17183580.33</v>
+        <v>29147315.1</v>
       </c>
       <c r="M641" t="n">
-        <v>17183580.33</v>
+        <v>29147315.1</v>
       </c>
       <c r="N641" t="n">
-        <v>14619000</v>
+        <v>21860486.4</v>
       </c>
     </row>
     <row r="642">
@@ -36313,7 +36313,7 @@
         </is>
       </c>
       <c r="F642" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G642" t="n">
         <v>10774</v>
@@ -36338,10 +36338,10 @@
         <v>29147315.1</v>
       </c>
       <c r="M642" t="n">
-        <v>29147315.1</v>
+        <v>0</v>
       </c>
       <c r="N642" t="n">
-        <v>21860486.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="643">
@@ -36350,54 +36350,54 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>2301520 000031/2025</t>
+          <t>2301520 000032/2025</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>9481581</t>
+          <t>9479677</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>DC-9481581/2025</t>
+          <t>DC-9479677/2025</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
+          <t>CROS CONSTRUCOES S/A</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G643" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I643" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K643" t="n">
         <v>1</v>
       </c>
       <c r="L643" t="n">
-        <v>29147315.1</v>
+        <v>65309420.72</v>
       </c>
       <c r="M643" t="n">
-        <v>0</v>
+        <v>65309420.72</v>
       </c>
       <c r="N643" t="n">
-        <v>0</v>
+        <v>57467603.75</v>
       </c>
     </row>
     <row r="644">
@@ -36406,22 +36406,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>2301520 000032/2025</t>
+          <t>2301520 000038/2025</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>9479677</t>
+          <t>9492083</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>DC-9479677/2025</t>
+          <t>DC-9492083/2025</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>CROS CONSTRUCOES S/A</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -36447,13 +36447,13 @@
         <v>1</v>
       </c>
       <c r="L644" t="n">
-        <v>65309420.72</v>
+        <v>74235570.89</v>
       </c>
       <c r="M644" t="n">
-        <v>65309420.72</v>
+        <v>74235570.89</v>
       </c>
       <c r="N644" t="n">
-        <v>57467603.75</v>
+        <v>59890000</v>
       </c>
     </row>
     <row r="645">
@@ -36462,54 +36462,54 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>2301520 000038/2025</t>
+          <t>2301601 000002/2025</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>9492083</t>
+          <t>9470883</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>DC-9492083/2025</t>
+          <t>DPEI-9470883</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>DYNATEST ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F645" t="n">
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>1740</v>
+        <v>10693</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS DE ENGENHARIA.</t>
         </is>
       </c>
       <c r="I645" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K645" t="n">
         <v>1</v>
       </c>
       <c r="L645" t="n">
-        <v>74235570.89</v>
+        <v>34605227.68</v>
       </c>
       <c r="M645" t="n">
-        <v>74235570.89</v>
+        <v>34605227.68</v>
       </c>
       <c r="N645" t="n">
-        <v>59890000</v>
+        <v>25953920.64</v>
       </c>
     </row>
     <row r="646">
@@ -36518,33 +36518,33 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>2301601 000002/2025</t>
+          <t>2301601 000003/2025</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>9470883</t>
+          <t>9470151</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>DPEI-9470883</t>
+          <t>DPEI-9470151</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>DYNATEST ENGENHARIA LTDA</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F646" t="n">
         <v>1</v>
       </c>
       <c r="G646" t="n">
-        <v>10693</v>
+        <v>46850</v>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS DE ENGENHARIA.</t>
+          <t>SERVICO GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS DEENGENHARIA</t>
         </is>
       </c>
       <c r="I646" t="n">
@@ -36559,13 +36559,13 @@
         <v>1</v>
       </c>
       <c r="L646" t="n">
-        <v>34605227.68</v>
+        <v>28087551.11</v>
       </c>
       <c r="M646" t="n">
-        <v>34605227.68</v>
+        <v>28087551.11</v>
       </c>
       <c r="N646" t="n">
-        <v>25953920.64</v>
+        <v>22458906.7</v>
       </c>
     </row>
     <row r="647">
@@ -36574,54 +36574,54 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>2301601 000003/2025</t>
+          <t>2301601 000004/2024</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>9470151</t>
+          <t>9447985</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>DPEI-9470151</t>
+          <t>DPEI-9447985</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>HOUER ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F647" t="n">
         <v>1</v>
       </c>
       <c r="G647" t="n">
-        <v>46850</v>
+        <v>23159</v>
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>SERVICO GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS DEENGENHARIA</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I647" t="n">
-        <v>3951</v>
+        <v>3981</v>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K647" t="n">
         <v>1</v>
       </c>
       <c r="L647" t="n">
-        <v>28087551.11</v>
+        <v>6361273.94</v>
       </c>
       <c r="M647" t="n">
-        <v>28087551.11</v>
+        <v>6361273.94</v>
       </c>
       <c r="N647" t="n">
-        <v>22458906.7</v>
+        <v>2540551.02</v>
       </c>
     </row>
     <row r="648">
@@ -36630,54 +36630,50 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>2301601 000004/2024</t>
+          <t>2301601 000004/2025</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>9447985</t>
-        </is>
-      </c>
-      <c r="D648" t="inlineStr">
-        <is>
-          <t>DPEI-9447985</t>
-        </is>
-      </c>
+          <t>9478110</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr">
         <is>
-          <t>HOUER ENGENHARIA LTDA</t>
+          <t>FUNDACAO GETULIO VARGAS</t>
         </is>
       </c>
       <c r="F648" t="n">
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>23159</v>
+        <v>26883</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I648" t="n">
-        <v>3981</v>
+        <v>3502</v>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K648" t="n">
         <v>1</v>
       </c>
       <c r="L648" t="n">
-        <v>6361273.94</v>
+        <v>22278613.12</v>
       </c>
       <c r="M648" t="n">
-        <v>6361273.94</v>
+        <v>22278613.12</v>
       </c>
       <c r="N648" t="n">
-        <v>2540551.02</v>
+        <v>22278613.12</v>
       </c>
     </row>
     <row r="649">
@@ -36686,18 +36682,22 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>2301601 000004/2025</t>
+          <t>2301601 000005/2025</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>9478110</t>
-        </is>
-      </c>
-      <c r="D649" t="inlineStr"/>
+          <t>9478941</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>DPEI-9478941/2025</t>
+        </is>
+      </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>FUNDACAO GETULIO VARGAS</t>
+          <t>FUNDACAO CHRISTIANO OTTONI</t>
         </is>
       </c>
       <c r="F649" t="n">
@@ -36723,13 +36723,13 @@
         <v>1</v>
       </c>
       <c r="L649" t="n">
-        <v>22278613.12</v>
+        <v>2401689.3</v>
       </c>
       <c r="M649" t="n">
-        <v>22278613.12</v>
+        <v>2401689.3</v>
       </c>
       <c r="N649" t="n">
-        <v>22278613.12</v>
+        <v>2401689.3</v>
       </c>
     </row>
     <row r="650">
@@ -36738,54 +36738,54 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>2301601 000005/2025</t>
+          <t>2301617 000002/2025</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>9478941</t>
+          <t>9461425</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>DPEI-9478941/2025</t>
+          <t>AMA-9461425/2025</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>FUNDACAO CHRISTIANO OTTONI</t>
+          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
         </is>
       </c>
       <c r="F650" t="n">
         <v>1</v>
       </c>
       <c r="G650" t="n">
-        <v>26883</v>
+        <v>23167</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
         </is>
       </c>
       <c r="I650" t="n">
-        <v>3502</v>
+        <v>3999</v>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K650" t="n">
         <v>1</v>
       </c>
       <c r="L650" t="n">
-        <v>2401689.3</v>
+        <v>31713.27</v>
       </c>
       <c r="M650" t="n">
-        <v>2401689.3</v>
+        <v>31713.27</v>
       </c>
       <c r="N650" t="n">
-        <v>2401689.3</v>
+        <v>31713.27</v>
       </c>
     </row>
     <row r="651">
@@ -36835,13 +36835,13 @@
         <v>1</v>
       </c>
       <c r="L651" t="n">
-        <v>31713.27</v>
+        <v>38863.58</v>
       </c>
       <c r="M651" t="n">
-        <v>31713.27</v>
+        <v>38863.58</v>
       </c>
       <c r="N651" t="n">
-        <v>31713.27</v>
+        <v>38863.58</v>
       </c>
     </row>
     <row r="652">
@@ -36850,22 +36850,22 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>2301617 000002/2025</t>
+          <t>2301617 000004/2024</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>9461425</t>
+          <t>9447965</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>AMA-9461425/2025</t>
+          <t>AMA-9447965/2025</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
+          <t>DIRECAO CONSULTORIA E ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F652" t="n">
@@ -36891,13 +36891,13 @@
         <v>1</v>
       </c>
       <c r="L652" t="n">
-        <v>38863.58</v>
+        <v>965839.63</v>
       </c>
       <c r="M652" t="n">
-        <v>38863.58</v>
+        <v>965839.63</v>
       </c>
       <c r="N652" t="n">
-        <v>38863.58</v>
+        <v>924684.42</v>
       </c>
     </row>
     <row r="653">
@@ -36906,17 +36906,17 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>2301617 000004/2024</t>
+          <t>2301617 000005/2024</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>9447965</t>
+          <t>9458828</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>AMA-9447965/2025</t>
+          <t>AMA-9458828/2025</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -36947,13 +36947,13 @@
         <v>1</v>
       </c>
       <c r="L653" t="n">
-        <v>965839.63</v>
+        <v>839153.24</v>
       </c>
       <c r="M653" t="n">
-        <v>965839.63</v>
+        <v>839153.24</v>
       </c>
       <c r="N653" t="n">
-        <v>924684.42</v>
+        <v>803371.39</v>
       </c>
     </row>
     <row r="654">
@@ -36962,54 +36962,54 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>2301617 000005/2024</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>9458828</t>
+          <t>9471830</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>AMA-9458828/2025</t>
+          <t>DM-9471830/2025</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>DIRECAO CONSULTORIA E ENGENHARIA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F654" t="n">
         <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>23167</v>
+        <v>1872</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I654" t="n">
-        <v>3999</v>
+        <v>5107</v>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K654" t="n">
         <v>1</v>
       </c>
       <c r="L654" t="n">
-        <v>839153.24</v>
+        <v>75462448.56</v>
       </c>
       <c r="M654" t="n">
-        <v>839153.24</v>
+        <v>75462448.56</v>
       </c>
       <c r="N654" t="n">
-        <v>803371.39</v>
+        <v>53573999.99</v>
       </c>
     </row>
     <row r="655">
@@ -37023,17 +37023,17 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>9471830</t>
+          <t>9471832</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>DM-9471830/2025</t>
+          <t>DM-9471832/2025</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F655" t="n">
@@ -37059,13 +37059,13 @@
         <v>1</v>
       </c>
       <c r="L655" t="n">
-        <v>75462448.56</v>
+        <v>74549476.59</v>
       </c>
       <c r="M655" t="n">
-        <v>75462448.56</v>
+        <v>74549476.59</v>
       </c>
       <c r="N655" t="n">
-        <v>53573999.99</v>
+        <v>49093539.45</v>
       </c>
     </row>
     <row r="656">
@@ -37079,17 +37079,17 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>9471832</t>
+          <t>9471834</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>DM-9471832/2025</t>
+          <t>DM-9471834/2025</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
         </is>
       </c>
       <c r="F656" t="n">
@@ -37115,13 +37115,13 @@
         <v>1</v>
       </c>
       <c r="L656" t="n">
-        <v>74549476.59</v>
+        <v>71047185.15000001</v>
       </c>
       <c r="M656" t="n">
-        <v>74549476.59</v>
+        <v>71047185.15000001</v>
       </c>
       <c r="N656" t="n">
-        <v>49093539.45</v>
+        <v>50960749.38</v>
       </c>
     </row>
     <row r="657">
@@ -37135,17 +37135,17 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>9471834</t>
+          <t>9471835</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>DM-9471834/2025</t>
+          <t>DM-9471835/2025</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F657" t="n">
@@ -37171,13 +37171,13 @@
         <v>1</v>
       </c>
       <c r="L657" t="n">
-        <v>71047185.15000001</v>
+        <v>71318172.81999999</v>
       </c>
       <c r="M657" t="n">
-        <v>71047185.15000001</v>
+        <v>71318172.81999999</v>
       </c>
       <c r="N657" t="n">
-        <v>50960749.38</v>
+        <v>44573000</v>
       </c>
     </row>
     <row r="658">
@@ -37191,17 +37191,17 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>9471835</t>
+          <t>9471879</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>DM-9471835/2025</t>
+          <t>DM-9471879/2025</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>MA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F658" t="n">
@@ -37227,13 +37227,13 @@
         <v>1</v>
       </c>
       <c r="L658" t="n">
-        <v>71318172.81999999</v>
+        <v>80365266.31999999</v>
       </c>
       <c r="M658" t="n">
-        <v>71318172.81999999</v>
+        <v>80365266.31999999</v>
       </c>
       <c r="N658" t="n">
-        <v>44573000</v>
+        <v>53241874.38</v>
       </c>
     </row>
     <row r="659">
@@ -37247,17 +37247,17 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>9471879</t>
+          <t>9471880</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>DM-9471879/2025</t>
+          <t>DM-9471880/2025</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>MA ENGENHARIA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F659" t="n">
@@ -37283,13 +37283,13 @@
         <v>1</v>
       </c>
       <c r="L659" t="n">
-        <v>80365266.31999999</v>
+        <v>76047809.47</v>
       </c>
       <c r="M659" t="n">
-        <v>80365266.31999999</v>
+        <v>76047809.47</v>
       </c>
       <c r="N659" t="n">
-        <v>53241874.38</v>
+        <v>51814575.44</v>
       </c>
     </row>
     <row r="660">
@@ -37303,17 +37303,17 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>9471880</t>
+          <t>9471881</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>DM-9471880/2025</t>
+          <t>DM-9471881/2025</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CTC LTDA</t>
         </is>
       </c>
       <c r="F660" t="n">
@@ -37339,13 +37339,13 @@
         <v>1</v>
       </c>
       <c r="L660" t="n">
-        <v>76047809.47</v>
+        <v>76234321.51000001</v>
       </c>
       <c r="M660" t="n">
-        <v>76047809.47</v>
+        <v>76234321.51000001</v>
       </c>
       <c r="N660" t="n">
-        <v>51814575.44</v>
+        <v>53358800</v>
       </c>
     </row>
     <row r="661">
@@ -37359,17 +37359,17 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>9471881</t>
+          <t>9473163</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>DM-9471881/2025</t>
+          <t>DM-9473163/2025</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CTC LTDA</t>
+          <t>GUAXIMA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F661" t="n">
@@ -37395,13 +37395,13 @@
         <v>1</v>
       </c>
       <c r="L661" t="n">
-        <v>76234321.51000001</v>
+        <v>88896704.79000001</v>
       </c>
       <c r="M661" t="n">
-        <v>76234321.51000001</v>
+        <v>88896704.79000001</v>
       </c>
       <c r="N661" t="n">
-        <v>53358800</v>
+        <v>59299394.97</v>
       </c>
     </row>
     <row r="662">
@@ -37410,22 +37410,22 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301762 000004/2025</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>9473163</t>
+          <t>9473312</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>DM-9473163/2025</t>
+          <t>DM-9473312/2025</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>GUAXIMA ENGENHARIA LTDA</t>
+          <t>MATRIX INFRAESTRUTURA LTDA - 'EM RECUPERACAO JUDICIAL'</t>
         </is>
       </c>
       <c r="F662" t="n">
@@ -37451,13 +37451,13 @@
         <v>1</v>
       </c>
       <c r="L662" t="n">
-        <v>88896704.79000001</v>
+        <v>8322333.63</v>
       </c>
       <c r="M662" t="n">
-        <v>88896704.79000001</v>
+        <v>8322333.63</v>
       </c>
       <c r="N662" t="n">
-        <v>59299394.97</v>
+        <v>7074995.71</v>
       </c>
     </row>
     <row r="663">
@@ -37466,17 +37466,17 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>2301762 000004/2025</t>
+          <t>2301762 000005/2025</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>9473312</t>
+          <t>9474704</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>DM-9473312/2025</t>
+          <t>DM-9474704/2025</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -37507,13 +37507,13 @@
         <v>1</v>
       </c>
       <c r="L663" t="n">
-        <v>8322333.63</v>
+        <v>9663464.630000001</v>
       </c>
       <c r="M663" t="n">
-        <v>8322333.63</v>
+        <v>9663464.630000001</v>
       </c>
       <c r="N663" t="n">
-        <v>7074995.71</v>
+        <v>7710000</v>
       </c>
     </row>
     <row r="664">
@@ -37522,22 +37522,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>2301762 000005/2025</t>
+          <t>2301762 000016/2025</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>9474704</t>
+          <t>9485592</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>DM-9474704/2025</t>
+          <t>DM-9485592/2025</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>MATRIX INFRAESTRUTURA LTDA - 'EM RECUPERACAO JUDICIAL'</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -37563,13 +37563,13 @@
         <v>1</v>
       </c>
       <c r="L664" t="n">
-        <v>9663464.630000001</v>
+        <v>13962359.26</v>
       </c>
       <c r="M664" t="n">
-        <v>9663464.630000001</v>
+        <v>13962359.26</v>
       </c>
       <c r="N664" t="n">
-        <v>7710000</v>
+        <v>10929975.56</v>
       </c>
     </row>
     <row r="665">
@@ -37578,22 +37578,22 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>2301762 000016/2025</t>
+          <t>2301762 000017/2024</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>9485592</t>
+          <t>9447456</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>DM-9485592/2025</t>
+          <t>DM-9447456/2024</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -37619,13 +37619,13 @@
         <v>1</v>
       </c>
       <c r="L665" t="n">
-        <v>13962359.26</v>
+        <v>6557067.25</v>
       </c>
       <c r="M665" t="n">
-        <v>13962359.26</v>
+        <v>6557067.25</v>
       </c>
       <c r="N665" t="n">
-        <v>10929975.56</v>
+        <v>4917800.43</v>
       </c>
     </row>
     <row r="666">
@@ -37634,22 +37634,22 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>2301762 000017/2024</t>
+          <t>2301762 000017/2025</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>9447456</t>
+          <t>9485591</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>DM-9447456/2024</t>
+          <t>DM-9485591/2025</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -37675,13 +37675,13 @@
         <v>1</v>
       </c>
       <c r="L666" t="n">
-        <v>6557067.25</v>
+        <v>8331047.13</v>
       </c>
       <c r="M666" t="n">
-        <v>6557067.25</v>
+        <v>8331047.13</v>
       </c>
       <c r="N666" t="n">
-        <v>4917800.43</v>
+        <v>6199729.76</v>
       </c>
     </row>
     <row r="667">
@@ -37690,22 +37690,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>2301762 000017/2025</t>
+          <t>2301762 000018/2024</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>9485591</t>
+          <t>9454417</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>DM-9485591/2025</t>
+          <t>DM-9454417/2025</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F667" t="n">
@@ -37731,13 +37731,13 @@
         <v>1</v>
       </c>
       <c r="L667" t="n">
-        <v>8331047.13</v>
+        <v>38329183.15</v>
       </c>
       <c r="M667" t="n">
-        <v>8331047.13</v>
+        <v>38329183.15</v>
       </c>
       <c r="N667" t="n">
-        <v>6199729.76</v>
+        <v>28746887.36</v>
       </c>
     </row>
     <row r="668">
@@ -37746,22 +37746,22 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>2301762 000018/2024</t>
+          <t>2301762 000019/2024</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>9454417</t>
+          <t>9452477</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>DM-9454417/2025</t>
+          <t>DM-9452477/2025</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -37787,13 +37787,13 @@
         <v>1</v>
       </c>
       <c r="L668" t="n">
-        <v>38329183.15</v>
+        <v>52446095.99</v>
       </c>
       <c r="M668" t="n">
-        <v>38329183.15</v>
+        <v>52446095.99</v>
       </c>
       <c r="N668" t="n">
-        <v>28746887.36</v>
+        <v>39334571.99</v>
       </c>
     </row>
     <row r="669">
@@ -37802,22 +37802,22 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>2301762 000019/2024</t>
+          <t>2301762 000020/2024</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>9452477</t>
+          <t>9459013</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>DM-9452477/2025</t>
+          <t>DM-9459013/2025</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F669" t="n">
@@ -37843,13 +37843,13 @@
         <v>1</v>
       </c>
       <c r="L669" t="n">
-        <v>52446095.99</v>
+        <v>59309539.93</v>
       </c>
       <c r="M669" t="n">
-        <v>52446095.99</v>
+        <v>59309539.93</v>
       </c>
       <c r="N669" t="n">
-        <v>39334571.99</v>
+        <v>44482154.94</v>
       </c>
     </row>
     <row r="670">
@@ -37858,22 +37858,22 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>2301762 000020/2024</t>
+          <t>2301762 000021/2024</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>9459013</t>
+          <t>9453530</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>DM-9459013/2025</t>
+          <t>DM-9453530</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F670" t="n">
@@ -37899,13 +37899,13 @@
         <v>1</v>
       </c>
       <c r="L670" t="n">
-        <v>59309539.93</v>
+        <v>9479564.210000001</v>
       </c>
       <c r="M670" t="n">
-        <v>59309539.93</v>
+        <v>9479564.210000001</v>
       </c>
       <c r="N670" t="n">
-        <v>44482154.94</v>
+        <v>7109673.15</v>
       </c>
     </row>
     <row r="671">
@@ -37914,22 +37914,22 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>2301762 000021/2024</t>
+          <t>2301762 000024/2025</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>9453530</t>
+          <t>9492723</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>DM-9453530</t>
+          <t>DM-9492723/2025</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F671" t="n">
@@ -37955,13 +37955,13 @@
         <v>1</v>
       </c>
       <c r="L671" t="n">
-        <v>9479564.210000001</v>
+        <v>60200606.24</v>
       </c>
       <c r="M671" t="n">
-        <v>9479564.210000001</v>
+        <v>60200606.24</v>
       </c>
       <c r="N671" t="n">
-        <v>7109673.15</v>
+        <v>41984578.11</v>
       </c>
     </row>
     <row r="672">
@@ -37970,54 +37970,54 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>2301762 000024/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>9492723</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>DM-9492723/2025</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>RAUTAKI TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="F672" t="n">
         <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>1872</v>
+        <v>11207</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I672" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K672" t="n">
         <v>1</v>
       </c>
       <c r="L672" t="n">
-        <v>60200606.24</v>
+        <v>25269915.6</v>
       </c>
       <c r="M672" t="n">
-        <v>60200606.24</v>
+        <v>25269915.6</v>
       </c>
       <c r="N672" t="n">
-        <v>41984578.11</v>
+        <v>23434999.8</v>
       </c>
     </row>
     <row r="673">
@@ -38031,49 +38031,49 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DO009482014/2025</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>RAUTAKI TECNOLOGIA LTDA</t>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="F673" t="n">
         <v>1</v>
       </c>
       <c r="G673" t="n">
-        <v>11207</v>
+        <v>66419</v>
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
         </is>
       </c>
       <c r="I673" t="n">
-        <v>3951</v>
+        <v>3971</v>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
         </is>
       </c>
       <c r="K673" t="n">
         <v>1</v>
       </c>
       <c r="L673" t="n">
-        <v>25269915.6</v>
+        <v>87218202.05</v>
       </c>
       <c r="M673" t="n">
-        <v>25269915.6</v>
+        <v>87218202.05</v>
       </c>
       <c r="N673" t="n">
-        <v>23434999.8</v>
+        <v>77898894.3</v>
       </c>
     </row>
     <row r="674">
@@ -38092,7 +38092,7 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>DO009482014/2025</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -38143,17 +38143,17 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -38179,13 +38179,13 @@
         <v>1</v>
       </c>
       <c r="L675" t="n">
-        <v>87218202.05</v>
+        <v>79690903.56</v>
       </c>
       <c r="M675" t="n">
-        <v>87218202.05</v>
+        <v>79690903.56</v>
       </c>
       <c r="N675" t="n">
-        <v>77898894.3</v>
+        <v>47349998.43</v>
       </c>
     </row>
     <row r="676">
@@ -38199,17 +38199,17 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
+          <t>TALENTECH - TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -38235,13 +38235,13 @@
         <v>1</v>
       </c>
       <c r="L676" t="n">
-        <v>79690903.56</v>
+        <v>73884529.66</v>
       </c>
       <c r="M676" t="n">
-        <v>79690903.56</v>
+        <v>73884529.66</v>
       </c>
       <c r="N676" t="n">
-        <v>47349998.43</v>
+        <v>35989998.13</v>
       </c>
     </row>
     <row r="677">
@@ -38255,17 +38255,17 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>TALENTECH - TECNOLOGIA LTDA</t>
+          <t>ELISEU KOPP &amp; CIA LTDA</t>
         </is>
       </c>
       <c r="F677" t="n">
@@ -38291,13 +38291,13 @@
         <v>1</v>
       </c>
       <c r="L677" t="n">
-        <v>73884529.66</v>
+        <v>75334510.38</v>
       </c>
       <c r="M677" t="n">
-        <v>73884529.66</v>
+        <v>75334510.38</v>
       </c>
       <c r="N677" t="n">
-        <v>35989998.13</v>
+        <v>45188997.86</v>
       </c>
     </row>
     <row r="678">
@@ -38311,17 +38311,17 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>ELISEU KOPP &amp; CIA LTDA</t>
+          <t>DATA TRAFFIC S/A</t>
         </is>
       </c>
       <c r="F678" t="n">
@@ -38347,13 +38347,13 @@
         <v>1</v>
       </c>
       <c r="L678" t="n">
-        <v>75334510.38</v>
+        <v>65055206.84</v>
       </c>
       <c r="M678" t="n">
-        <v>75334510.38</v>
+        <v>65055206.84</v>
       </c>
       <c r="N678" t="n">
-        <v>45188997.86</v>
+        <v>32097999.96</v>
       </c>
     </row>
     <row r="679">
@@ -38362,54 +38362,54 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9468567</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>AEST-9468567/2025</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>DATA TRAFFIC S/A</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F679" t="n">
         <v>1</v>
       </c>
       <c r="G679" t="n">
-        <v>66419</v>
+        <v>26883</v>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I679" t="n">
-        <v>3971</v>
+        <v>3502</v>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K679" t="n">
         <v>1</v>
       </c>
       <c r="L679" t="n">
-        <v>65055206.84</v>
+        <v>12267717.16</v>
       </c>
       <c r="M679" t="n">
-        <v>65055206.84</v>
+        <v>12267717.16</v>
       </c>
       <c r="N679" t="n">
-        <v>32097999.96</v>
+        <v>9200787.869999999</v>
       </c>
     </row>
     <row r="680">
@@ -38423,17 +38423,17 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>9468567</t>
+          <t>9468573</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>AEST-9468567/2025</t>
+          <t>AEST-9468573/2025</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F680" t="n">
@@ -38459,13 +38459,13 @@
         <v>1</v>
       </c>
       <c r="L680" t="n">
-        <v>12267717.16</v>
+        <v>12291296.66</v>
       </c>
       <c r="M680" t="n">
-        <v>12267717.16</v>
+        <v>12291296.66</v>
       </c>
       <c r="N680" t="n">
-        <v>9200787.869999999</v>
+        <v>9218472.49</v>
       </c>
     </row>
     <row r="681">
@@ -38479,17 +38479,17 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>9468573</t>
+          <t>9468704</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>AEST-9468573/2025</t>
+          <t>AEST-9468704/2025</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F681" t="n">
@@ -38515,13 +38515,13 @@
         <v>1</v>
       </c>
       <c r="L681" t="n">
-        <v>12291296.66</v>
+        <v>12197245.67</v>
       </c>
       <c r="M681" t="n">
-        <v>12291296.66</v>
+        <v>12197245.67</v>
       </c>
       <c r="N681" t="n">
-        <v>9218472.49</v>
+        <v>9147934.25</v>
       </c>
     </row>
     <row r="682">
@@ -38535,17 +38535,17 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>9468704</t>
+          <t>9469794</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>AEST-9468704/2025</t>
+          <t xml:space="preserve"> AEST-9469794/2025</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="F682" t="n">
@@ -38571,13 +38571,13 @@
         <v>1</v>
       </c>
       <c r="L682" t="n">
-        <v>12197245.67</v>
+        <v>12379211.81</v>
       </c>
       <c r="M682" t="n">
-        <v>12197245.67</v>
+        <v>12379211.81</v>
       </c>
       <c r="N682" t="n">
-        <v>9147934.25</v>
+        <v>9284408.859999999</v>
       </c>
     </row>
     <row r="683">
@@ -38591,17 +38591,17 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>9469794</t>
+          <t>9470136</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>AEST-9469794/2025</t>
+          <t>AEST-9470136/2025</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
+          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
         </is>
       </c>
       <c r="F683" t="n">
@@ -38627,69 +38627,69 @@
         <v>1</v>
       </c>
       <c r="L683" t="n">
-        <v>12379211.81</v>
+        <v>12547127.86</v>
       </c>
       <c r="M683" t="n">
-        <v>12379211.81</v>
+        <v>12547127.86</v>
       </c>
       <c r="N683" t="n">
-        <v>9284408.859999999</v>
+        <v>9410345.9</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>9470136</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>AEST-9470136/2025</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
+          <t>PROCEC ENGENHARIA S.A</t>
         </is>
       </c>
       <c r="F684" t="n">
         <v>1</v>
       </c>
       <c r="G684" t="n">
-        <v>26883</v>
+        <v>1740</v>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I684" t="n">
-        <v>3502</v>
+        <v>5107</v>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K684" t="n">
         <v>1</v>
       </c>
       <c r="L684" t="n">
-        <v>12547127.86</v>
+        <v>5887057.98</v>
       </c>
       <c r="M684" t="n">
-        <v>12547127.86</v>
+        <v>5887057.98</v>
       </c>
       <c r="N684" t="n">
-        <v>9410345.9</v>
+        <v>5658828.94</v>
       </c>
     </row>
     <row r="685">
@@ -38698,22 +38698,22 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>PROCEC ENGENHARIA S.A</t>
+          <t>OPACO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -38739,13 +38739,13 @@
         <v>1</v>
       </c>
       <c r="L685" t="n">
-        <v>5887057.98</v>
+        <v>28204745.51</v>
       </c>
       <c r="M685" t="n">
-        <v>5887057.98</v>
+        <v>28204745.51</v>
       </c>
       <c r="N685" t="n">
-        <v>5658828.94</v>
+        <v>28204745.51</v>
       </c>
     </row>
     <row r="686">
@@ -38754,22 +38754,22 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>OPACO ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
         </is>
       </c>
       <c r="F686" t="n">
@@ -38795,13 +38795,13 @@
         <v>1</v>
       </c>
       <c r="L686" t="n">
-        <v>28204745.51</v>
+        <v>4383662.29</v>
       </c>
       <c r="M686" t="n">
-        <v>28204745.51</v>
+        <v>4383662.29</v>
       </c>
       <c r="N686" t="n">
-        <v>28204745.51</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="687">
@@ -38810,22 +38810,18 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>9497471</t>
-        </is>
-      </c>
-      <c r="D687" t="inlineStr">
-        <is>
-          <t>DC-9497471/2026</t>
-        </is>
-      </c>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F687" t="n">
@@ -38848,16 +38844,16 @@
         </is>
       </c>
       <c r="K687" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L687" t="n">
-        <v>4383662.29</v>
+        <v>19733859.27</v>
       </c>
       <c r="M687" t="n">
-        <v>4383662.29</v>
+        <v>19733859.26</v>
       </c>
       <c r="N687" t="n">
-        <v>3700000</v>
+        <v>16179998.72</v>
       </c>
     </row>
     <row r="688">
@@ -38866,22 +38862,18 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>9511902</t>
-        </is>
-      </c>
-      <c r="D688" t="inlineStr">
-        <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
+          <t>9515457</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr"/>
       <c r="E688" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F688" t="n">
@@ -38904,16 +38896,16 @@
         </is>
       </c>
       <c r="K688" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L688" t="n">
-        <v>19733859.27</v>
+        <v>120767701.47</v>
       </c>
       <c r="M688" t="n">
-        <v>19733859.26</v>
+        <v>120767701.47</v>
       </c>
       <c r="N688" t="n">
-        <v>16179998.72</v>
+        <v>87996201.20999999</v>
       </c>
     </row>
     <row r="689">
@@ -38922,17 +38914,17 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301520 000010/2026</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9498942</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DC-011R/2024</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
@@ -38960,16 +38952,16 @@
         </is>
       </c>
       <c r="K689" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L689" t="n">
-        <v>120767701.47</v>
+        <v>2962697.76</v>
       </c>
       <c r="M689" t="n">
-        <v>120767701.47</v>
+        <v>2962697.76</v>
       </c>
       <c r="N689" t="n">
-        <v>87996201.20999999</v>
+        <v>2962697.76</v>
       </c>
     </row>
     <row r="690">
@@ -38978,22 +38970,22 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>2301520 000010/2026</t>
+          <t>2301520 000030/2025</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>9498942</t>
+          <t>9495596</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>DC-011R/2024</t>
+          <t>DC-9495596/2026</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F690" t="n">
@@ -39019,13 +39011,13 @@
         <v>1</v>
       </c>
       <c r="L690" t="n">
-        <v>2962697.76</v>
+        <v>15970367.44</v>
       </c>
       <c r="M690" t="n">
-        <v>2962697.76</v>
+        <v>15970367.44</v>
       </c>
       <c r="N690" t="n">
-        <v>2962697.76</v>
+        <v>12246077.75</v>
       </c>
     </row>
     <row r="691">
@@ -39034,54 +39026,54 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>2301520 000030/2025</t>
+          <t>2301520 000034/2025</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>9495596</t>
+          <t>9493122</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>DC-9495596/2026</t>
+          <t>DC-9493122/2026</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F691" t="n">
         <v>1</v>
       </c>
       <c r="G691" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I691" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K691" t="n">
         <v>1</v>
       </c>
       <c r="L691" t="n">
-        <v>15970367.44</v>
+        <v>7420078.73</v>
       </c>
       <c r="M691" t="n">
-        <v>15970367.44</v>
+        <v>7420078.73</v>
       </c>
       <c r="N691" t="n">
-        <v>12246077.75</v>
+        <v>6677404.33</v>
       </c>
     </row>
     <row r="692">
@@ -39090,17 +39082,17 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>2301520 000034/2025</t>
+          <t>2301520 000035/2025</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>9493122</t>
+          <t>9492715</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>DC-9493122/2026</t>
+          <t>DC-9492715/2025</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -39131,13 +39123,13 @@
         <v>1</v>
       </c>
       <c r="L692" t="n">
-        <v>7420078.73</v>
+        <v>3563439</v>
       </c>
       <c r="M692" t="n">
-        <v>7420078.73</v>
+        <v>3563439</v>
       </c>
       <c r="N692" t="n">
-        <v>6677404.33</v>
+        <v>3028048.96</v>
       </c>
     </row>
     <row r="693">
@@ -39146,54 +39138,54 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>2301520 000035/2025</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>9492715</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>DC-9492715/2025</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CONTORNO LTDA</t>
         </is>
       </c>
       <c r="F693" t="n">
         <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I693" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K693" t="n">
         <v>1</v>
       </c>
       <c r="L693" t="n">
-        <v>3563439</v>
+        <v>44004328.59</v>
       </c>
       <c r="M693" t="n">
-        <v>3563439</v>
+        <v>44004328.59</v>
       </c>
       <c r="N693" t="n">
-        <v>3028048.96</v>
+        <v>37600000</v>
       </c>
     </row>
     <row r="694">
@@ -39202,22 +39194,22 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CONTORNO LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F694" t="n">
@@ -39240,16 +39232,16 @@
         </is>
       </c>
       <c r="K694" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L694" t="n">
-        <v>44004328.59</v>
+        <v>11144418.23</v>
       </c>
       <c r="M694" t="n">
-        <v>44004328.59</v>
+        <v>11144418.22</v>
       </c>
       <c r="N694" t="n">
-        <v>37600000</v>
+        <v>9814000</v>
       </c>
     </row>
     <row r="695">
@@ -39258,54 +39250,50 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>9501601</t>
-        </is>
-      </c>
-      <c r="D695" t="inlineStr">
-        <is>
-          <t>DC-9501601/2026</t>
-        </is>
-      </c>
+          <t>9498666</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr"/>
       <c r="E695" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>DYNATEST ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F695" t="n">
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I695" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K695" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L695" t="n">
-        <v>11144418.23</v>
+        <v>32765091.84</v>
       </c>
       <c r="M695" t="n">
-        <v>11144418.22</v>
+        <v>32765091.84</v>
       </c>
       <c r="N695" t="n">
-        <v>9814000</v>
+        <v>23052682.68</v>
       </c>
     </row>
     <row r="696">
@@ -39314,50 +39302,50 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301520 000042/2025</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>9498666</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="D696" t="inlineStr"/>
       <c r="E696" t="inlineStr">
         <is>
-          <t>DYNATEST ENGENHARIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F696" t="n">
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>11207</v>
+        <v>10774</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I696" t="n">
-        <v>3951</v>
+        <v>5106</v>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K696" t="n">
         <v>1</v>
       </c>
       <c r="L696" t="n">
-        <v>32765091.84</v>
+        <v>6323844.01</v>
       </c>
       <c r="M696" t="n">
-        <v>32765091.84</v>
+        <v>6323844.01</v>
       </c>
       <c r="N696" t="n">
-        <v>23052682.68</v>
+        <v>4742883</v>
       </c>
     </row>
     <row r="697">
@@ -39366,54 +39354,54 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2301520 000042/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>9501894</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F697" t="n">
         <v>1</v>
       </c>
       <c r="G697" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I697" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K697" t="n">
         <v>1</v>
       </c>
       <c r="L697" t="n">
-        <v>6323844.01</v>
+        <v>3965005.14</v>
       </c>
       <c r="M697" t="n">
-        <v>6323844.01</v>
+        <v>3965005.14</v>
       </c>
       <c r="N697" t="n">
-        <v>4742883</v>
+        <v>2961858.83</v>
       </c>
     </row>
     <row r="698">
@@ -39422,22 +39410,18 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>9505062</t>
-        </is>
-      </c>
-      <c r="D698" t="inlineStr">
-        <is>
-          <t>DC-9505062/2026</t>
-        </is>
-      </c>
+          <t>9518766</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>MAIS CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="F698" t="n">
@@ -39463,13 +39447,13 @@
         <v>1</v>
       </c>
       <c r="L698" t="n">
-        <v>3965005.14</v>
+        <v>151298828.22</v>
       </c>
       <c r="M698" t="n">
-        <v>3965005.14</v>
+        <v>151298828.22</v>
       </c>
       <c r="N698" t="n">
-        <v>2961858.83</v>
+        <v>120800000</v>
       </c>
     </row>
     <row r="699">
@@ -39478,54 +39462,54 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>MAIS CONSTRUTORA LTDA</t>
+          <t>STE SERVICOS TECNICOS DE ENGENHARIA SA</t>
         </is>
       </c>
       <c r="F699" t="n">
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>1740</v>
+        <v>115827</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t xml:space="preserve">SERVICOS TECNICOS EM AREA AMBIENTAL </t>
         </is>
       </c>
       <c r="I699" t="n">
-        <v>5107</v>
+        <v>3973</v>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
         </is>
       </c>
       <c r="K699" t="n">
         <v>1</v>
       </c>
       <c r="L699" t="n">
-        <v>151298828.22</v>
+        <v>48044257.29</v>
       </c>
       <c r="M699" t="n">
-        <v>151298828.22</v>
+        <v>48044257.29</v>
       </c>
       <c r="N699" t="n">
-        <v>120800000</v>
+        <v>36033198.22</v>
       </c>
     </row>
     <row r="700">
@@ -39534,54 +39518,54 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301617 000004/2025</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9502187</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>STE SERVICOS TECNICOS DE ENGENHARIA SA</t>
+          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
         </is>
       </c>
       <c r="F700" t="n">
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>115827</v>
+        <v>23167</v>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICOS TECNICOS EM AREA AMBIENTAL </t>
+          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
         </is>
       </c>
       <c r="I700" t="n">
-        <v>3973</v>
+        <v>3999</v>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
+          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K700" t="n">
         <v>1</v>
       </c>
       <c r="L700" t="n">
-        <v>48044257.29</v>
+        <v>1904028.2</v>
       </c>
       <c r="M700" t="n">
-        <v>48044257.29</v>
+        <v>1904028.2</v>
       </c>
       <c r="N700" t="n">
-        <v>36033198.22</v>
+        <v>1768342.65</v>
       </c>
     </row>
     <row r="701">
@@ -39590,54 +39574,54 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2301617 000004/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>9502187</t>
+          <t>9493180</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>AMA-9502187/2026</t>
+          <t>DM-9493180/2026</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="F701" t="n">
         <v>1</v>
       </c>
       <c r="G701" t="n">
-        <v>23167</v>
+        <v>1872</v>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I701" t="n">
-        <v>3999</v>
+        <v>5107</v>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K701" t="n">
         <v>1</v>
       </c>
       <c r="L701" t="n">
-        <v>1904028.2</v>
+        <v>99982008.22</v>
       </c>
       <c r="M701" t="n">
-        <v>1904028.2</v>
+        <v>99982008.22</v>
       </c>
       <c r="N701" t="n">
-        <v>1768342.65</v>
+        <v>64984305.34</v>
       </c>
     </row>
     <row r="702">
@@ -39646,22 +39630,18 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>9493180</t>
-        </is>
-      </c>
-      <c r="D702" t="inlineStr">
-        <is>
-          <t>DM-9493180/2026</t>
-        </is>
-      </c>
+          <t>9512044</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F702" t="n">
@@ -39687,13 +39667,13 @@
         <v>1</v>
       </c>
       <c r="L702" t="n">
-        <v>99982008.22</v>
+        <v>13602005.38</v>
       </c>
       <c r="M702" t="n">
-        <v>99982008.22</v>
+        <v>13602005.38</v>
       </c>
       <c r="N702" t="n">
-        <v>64984305.34</v>
+        <v>11358610.11</v>
       </c>
     </row>
     <row r="703">
@@ -39702,22 +39682,18 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2301762 000001/2026</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>9512044</t>
-        </is>
-      </c>
-      <c r="D703" t="inlineStr">
-        <is>
-          <t>DM-9512044/2026</t>
-        </is>
-      </c>
+          <t>9512043</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F703" t="n">
@@ -39743,13 +39719,13 @@
         <v>1</v>
       </c>
       <c r="L703" t="n">
-        <v>13602005.38</v>
+        <v>73340224.20999999</v>
       </c>
       <c r="M703" t="n">
-        <v>13602005.38</v>
+        <v>73340224.20999999</v>
       </c>
       <c r="N703" t="n">
-        <v>11358610.11</v>
+        <v>44002130</v>
       </c>
     </row>
     <row r="704">
@@ -39758,22 +39734,22 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2301762 000004/2026</t>
+          <t>2301762 000022/2025</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>9512043</t>
+          <t>9493137</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>DM-9493137/2026</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>CONSTRUTORA ITAMARACA LTDA</t>
         </is>
       </c>
       <c r="F704" t="n">
@@ -39799,13 +39775,13 @@
         <v>1</v>
       </c>
       <c r="L704" t="n">
-        <v>73340224.20999999</v>
+        <v>11437822.96</v>
       </c>
       <c r="M704" t="n">
-        <v>73340224.20999999</v>
+        <v>11437822.96</v>
       </c>
       <c r="N704" t="n">
-        <v>44002130</v>
+        <v>10619818.83</v>
       </c>
     </row>
     <row r="705">
@@ -39814,22 +39790,22 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>2301762 000022/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>9493137</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>DM-9493137/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ITAMARACA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F705" t="n">
@@ -39855,13 +39831,13 @@
         <v>1</v>
       </c>
       <c r="L705" t="n">
-        <v>11437822.96</v>
+        <v>19019690.63</v>
       </c>
       <c r="M705" t="n">
-        <v>11437822.96</v>
+        <v>19019690.63</v>
       </c>
       <c r="N705" t="n">
-        <v>10619818.83</v>
+        <v>14264750.82</v>
       </c>
     </row>
     <row r="706">
@@ -39870,22 +39846,22 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301762 000025/2025</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9493202</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DM-9493202/2026</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F706" t="n">
@@ -39911,13 +39887,13 @@
         <v>1</v>
       </c>
       <c r="L706" t="n">
-        <v>19019690.63</v>
+        <v>6305546.68</v>
       </c>
       <c r="M706" t="n">
-        <v>19019690.63</v>
+        <v>6305546.68</v>
       </c>
       <c r="N706" t="n">
-        <v>14264750.82</v>
+        <v>4557819.64</v>
       </c>
     </row>
     <row r="707">
@@ -39926,54 +39902,54 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>2301762 000025/2025</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>9493202</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>DM-9493202/2026</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F707" t="n">
         <v>1</v>
       </c>
       <c r="G707" t="n">
-        <v>1872</v>
+        <v>8125</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
         </is>
       </c>
       <c r="I707" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K707" t="n">
         <v>1</v>
       </c>
       <c r="L707" t="n">
-        <v>6305546.68</v>
+        <v>8281446.48</v>
       </c>
       <c r="M707" t="n">
-        <v>6305546.68</v>
+        <v>0</v>
       </c>
       <c r="N707" t="n">
-        <v>4557819.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="708">
@@ -40012,11 +39988,11 @@
         </is>
       </c>
       <c r="I708" t="n">
-        <v>3951</v>
+        <v>5106</v>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K708" t="n">
@@ -40026,10 +40002,10 @@
         <v>8281446.48</v>
       </c>
       <c r="M708" t="n">
-        <v>0</v>
+        <v>8281446.48</v>
       </c>
       <c r="N708" t="n">
-        <v>0</v>
+        <v>5342582.88</v>
       </c>
     </row>
     <row r="709">
@@ -40038,54 +40014,50 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>9502116</t>
-        </is>
-      </c>
-      <c r="D709" t="inlineStr">
-        <is>
-          <t>DM-9502116/2026</t>
-        </is>
-      </c>
+          <t>9500304</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr"/>
       <c r="E709" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F709" t="n">
         <v>1</v>
       </c>
       <c r="G709" t="n">
-        <v>8125</v>
+        <v>1872</v>
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I709" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K709" t="n">
         <v>1</v>
       </c>
       <c r="L709" t="n">
-        <v>8281446.48</v>
+        <v>16936267.4</v>
       </c>
       <c r="M709" t="n">
-        <v>8281446.48</v>
+        <v>16936267.4</v>
       </c>
       <c r="N709" t="n">
-        <v>5342582.88</v>
+        <v>14124998.39</v>
       </c>
     </row>
     <row r="710">
@@ -40094,22 +40066,22 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>EMCONBRAS EMPRESA DE CONSERVACAO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="F710" t="n">
@@ -40135,13 +40107,13 @@
         <v>1</v>
       </c>
       <c r="L710" t="n">
-        <v>16936267.4</v>
+        <v>28640371.76</v>
       </c>
       <c r="M710" t="n">
-        <v>16936267.4</v>
+        <v>28640371.76</v>
       </c>
       <c r="N710" t="n">
-        <v>14124998.39</v>
+        <v>19798000</v>
       </c>
     </row>
     <row r="711">
@@ -40150,117 +40122,111 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPRESA DE CONSERVACAO BRASILEIRA LTDA</t>
+          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
         </is>
       </c>
       <c r="F711" t="n">
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>1872</v>
+        <v>66419</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
         </is>
       </c>
       <c r="I711" t="n">
-        <v>5107</v>
+        <v>3971</v>
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
         </is>
       </c>
       <c r="K711" t="n">
         <v>1</v>
       </c>
       <c r="L711" t="n">
-        <v>28640371.76</v>
+        <v>64031795.21</v>
       </c>
       <c r="M711" t="n">
-        <v>28640371.76</v>
+        <v>64031795.21</v>
       </c>
       <c r="N711" t="n">
-        <v>19798000</v>
+        <v>31699998.96</v>
       </c>
     </row>
     <row r="712">
-      <c r="A712" t="n">
-        <v>2026</v>
-      </c>
+      <c r="A712" t="inlineStr"/>
       <c r="B712" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000001/2020</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>9493205</t>
-        </is>
-      </c>
-      <c r="D712" t="inlineStr">
-        <is>
-          <t>DO-9493205/2026-L4</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr"/>
       <c r="E712" t="inlineStr">
         <is>
-          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F712" t="n">
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>66419</v>
+        <v>1740</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I712" t="n">
-        <v>3971</v>
+        <v>5107</v>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K712" t="n">
         <v>1</v>
       </c>
       <c r="L712" t="n">
-        <v>64031795.21</v>
+        <v>4668587.23</v>
       </c>
       <c r="M712" t="n">
-        <v>64031795.21</v>
+        <v>0</v>
       </c>
       <c r="N712" t="n">
-        <v>31699998.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr"/>
       <c r="B713" t="inlineStr">
         <is>
-          <t>2301520 000001/2020</t>
+          <t>2301520 000001/2021</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -40271,7 +40237,7 @@
       <c r="D713" t="inlineStr"/>
       <c r="E713" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F713" t="n">
@@ -40297,20 +40263,20 @@
         <v>1</v>
       </c>
       <c r="L713" t="n">
-        <v>4668587.23</v>
+        <v>16217686.32</v>
       </c>
       <c r="M713" t="n">
-        <v>0</v>
+        <v>16217686.32</v>
       </c>
       <c r="N713" t="n">
-        <v>0</v>
+        <v>12796116.03</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr"/>
       <c r="B714" t="inlineStr">
         <is>
-          <t>2301520 000001/2021</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -40321,7 +40287,7 @@
       <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F714" t="n">
@@ -40344,23 +40310,23 @@
         </is>
       </c>
       <c r="K714" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L714" t="n">
-        <v>16217686.32</v>
+        <v>18465630.31</v>
       </c>
       <c r="M714" t="n">
-        <v>16217686.32</v>
+        <v>0</v>
       </c>
       <c r="N714" t="n">
-        <v>12796116.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr"/>
       <c r="B715" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301520 000006/2020</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -40371,18 +40337,18 @@
       <c r="D715" t="inlineStr"/>
       <c r="E715" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F715" t="n">
         <v>1</v>
       </c>
       <c r="G715" t="n">
-        <v>1740</v>
+        <v>1872</v>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I715" t="n">
@@ -40394,23 +40360,23 @@
         </is>
       </c>
       <c r="K715" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L715" t="n">
-        <v>18465630.31</v>
+        <v>46371045.53</v>
       </c>
       <c r="M715" t="n">
-        <v>0</v>
+        <v>46371045.53</v>
       </c>
       <c r="N715" t="n">
-        <v>0</v>
+        <v>34303736.06</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr"/>
       <c r="B716" t="inlineStr">
         <is>
-          <t>2301520 000006/2020</t>
+          <t>2301520 000013/2021</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -40421,18 +40387,18 @@
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
         </is>
       </c>
       <c r="F716" t="n">
         <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>1872</v>
+        <v>1740</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I716" t="n">
@@ -40447,20 +40413,20 @@
         <v>1</v>
       </c>
       <c r="L716" t="n">
-        <v>46371045.53</v>
+        <v>2022624.54</v>
       </c>
       <c r="M716" t="n">
-        <v>46371045.53</v>
+        <v>2022624.54</v>
       </c>
       <c r="N716" t="n">
-        <v>34303736.06</v>
+        <v>1704806.45</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr"/>
       <c r="B717" t="inlineStr">
         <is>
-          <t>2301520 000013/2021</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -40471,39 +40437,39 @@
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr">
         <is>
-          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="F717" t="n">
         <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>1740</v>
+        <v>108600</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
         </is>
       </c>
       <c r="I717" t="n">
-        <v>5107</v>
+        <v>3964</v>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
         </is>
       </c>
       <c r="K717" t="n">
         <v>1</v>
       </c>
       <c r="L717" t="n">
-        <v>2022624.54</v>
+        <v>540000</v>
       </c>
       <c r="M717" t="n">
-        <v>2022624.54</v>
+        <v>540000</v>
       </c>
       <c r="N717" t="n">
-        <v>1704806.45</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="718">
@@ -40521,7 +40487,7 @@
       <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F718" t="n">
@@ -40547,13 +40513,13 @@
         <v>1</v>
       </c>
       <c r="L718" t="n">
-        <v>540000</v>
+        <v>454999.67</v>
       </c>
       <c r="M718" t="n">
-        <v>540000</v>
+        <v>454999.67</v>
       </c>
       <c r="N718" t="n">
-        <v>540000</v>
+        <v>454999.67</v>
       </c>
     </row>
     <row r="719">
@@ -40597,13 +40563,13 @@
         <v>1</v>
       </c>
       <c r="L719" t="n">
-        <v>454999.67</v>
+        <v>508997.33</v>
       </c>
       <c r="M719" t="n">
-        <v>454999.67</v>
+        <v>508997.33</v>
       </c>
       <c r="N719" t="n">
-        <v>454999.67</v>
+        <v>508997.33</v>
       </c>
     </row>
     <row r="720">
@@ -40621,7 +40587,7 @@
       <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F720" t="n">
@@ -40647,13 +40613,13 @@
         <v>1</v>
       </c>
       <c r="L720" t="n">
-        <v>508997.33</v>
+        <v>386990</v>
       </c>
       <c r="M720" t="n">
-        <v>508997.33</v>
+        <v>386990</v>
       </c>
       <c r="N720" t="n">
-        <v>508997.33</v>
+        <v>386990</v>
       </c>
     </row>
     <row r="721">
@@ -40671,7 +40637,7 @@
       <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="F721" t="n">
@@ -40697,13 +40663,13 @@
         <v>1</v>
       </c>
       <c r="L721" t="n">
-        <v>386990</v>
+        <v>384900</v>
       </c>
       <c r="M721" t="n">
-        <v>386990</v>
+        <v>384900</v>
       </c>
       <c r="N721" t="n">
-        <v>386990</v>
+        <v>384900</v>
       </c>
     </row>
     <row r="722">
@@ -40747,20 +40713,20 @@
         <v>1</v>
       </c>
       <c r="L722" t="n">
-        <v>384900</v>
+        <v>566000</v>
       </c>
       <c r="M722" t="n">
-        <v>384900</v>
+        <v>566000</v>
       </c>
       <c r="N722" t="n">
-        <v>384900</v>
+        <v>566000</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr"/>
       <c r="B723" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -40771,39 +40737,39 @@
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F723" t="n">
         <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>108600</v>
+        <v>23159</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I723" t="n">
-        <v>3964</v>
+        <v>3981</v>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K723" t="n">
         <v>1</v>
       </c>
       <c r="L723" t="n">
-        <v>566000</v>
+        <v>1947867.48</v>
       </c>
       <c r="M723" t="n">
-        <v>566000</v>
+        <v>0</v>
       </c>
       <c r="N723" t="n">
-        <v>566000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="724">
@@ -40847,7 +40813,7 @@
         <v>1</v>
       </c>
       <c r="L724" t="n">
-        <v>1947867.48</v>
+        <v>2235628.88</v>
       </c>
       <c r="M724" t="n">
         <v>0</v>
@@ -40897,7 +40863,7 @@
         <v>1</v>
       </c>
       <c r="L725" t="n">
-        <v>2235628.88</v>
+        <v>2251859.48</v>
       </c>
       <c r="M725" t="n">
         <v>0</v>
@@ -40910,7 +40876,7 @@
       <c r="A726" t="inlineStr"/>
       <c r="B726" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>2301762 000005/2023</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -40921,46 +40887,46 @@
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
         </is>
       </c>
       <c r="F726" t="n">
         <v>1</v>
       </c>
       <c r="G726" t="n">
-        <v>23159</v>
+        <v>1872</v>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I726" t="n">
-        <v>3981</v>
+        <v>5107</v>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K726" t="n">
         <v>1</v>
       </c>
       <c r="L726" t="n">
-        <v>2251859.48</v>
+        <v>10768247.16</v>
       </c>
       <c r="M726" t="n">
-        <v>0</v>
+        <v>10768247.16</v>
       </c>
       <c r="N726" t="n">
-        <v>0</v>
+        <v>8795462.050000001</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr"/>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2301762 000005/2023</t>
+          <t>2301762 000016/2017</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -40971,7 +40937,7 @@
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr">
         <is>
-          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
+          <t>DIEFRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F727" t="n">
@@ -40997,13 +40963,13 @@
         <v>1</v>
       </c>
       <c r="L727" t="n">
-        <v>10768247.16</v>
+        <v>24277046.87</v>
       </c>
       <c r="M727" t="n">
-        <v>10768247.16</v>
+        <v>24277046.87</v>
       </c>
       <c r="N727" t="n">
-        <v>8795462.050000001</v>
+        <v>24277046.87</v>
       </c>
     </row>
     <row r="728">
@@ -41021,7 +40987,7 @@
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr">
         <is>
-          <t>DIEFRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="F728" t="n">
@@ -41047,62 +41013,12 @@
         <v>1</v>
       </c>
       <c r="L728" t="n">
-        <v>24277046.87</v>
+        <v>12102613.88</v>
       </c>
       <c r="M728" t="n">
-        <v>24277046.87</v>
+        <v>12102613.88</v>
       </c>
       <c r="N728" t="n">
-        <v>24277046.87</v>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr"/>
-      <c r="B729" t="inlineStr">
-        <is>
-          <t>2301762 000016/2017</t>
-        </is>
-      </c>
-      <c r="C729" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D729" t="inlineStr"/>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
-        </is>
-      </c>
-      <c r="F729" t="n">
-        <v>1</v>
-      </c>
-      <c r="G729" t="n">
-        <v>1872</v>
-      </c>
-      <c r="H729" t="inlineStr">
-        <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
-        </is>
-      </c>
-      <c r="I729" t="n">
-        <v>5107</v>
-      </c>
-      <c r="J729" t="inlineStr">
-        <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
-        </is>
-      </c>
-      <c r="K729" t="n">
-        <v>1</v>
-      </c>
-      <c r="L729" t="n">
-        <v>12102613.88</v>
-      </c>
-      <c r="M729" t="n">
-        <v>12102613.88</v>
-      </c>
-      <c r="N729" t="n">
         <v>12102613.88</v>
       </c>
     </row>

--- a/upload/itens.xlsx
+++ b/upload/itens.xlsx
@@ -38540,7 +38540,7 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AEST-9469794/2025</t>
+          <t>AEST-9469794/2025</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -38818,7 +38818,11 @@
           <t>9511902</t>
         </is>
       </c>
-      <c r="D687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
       <c r="E687" t="inlineStr">
         <is>
           <t>LCM CONSTRUCAO E COMERCIO S.A</t>
@@ -38870,7 +38874,11 @@
           <t>9515457</t>
         </is>
       </c>
-      <c r="D688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
       <c r="E688" t="inlineStr">
         <is>
           <t>HWN ENGENHARIA LTDA</t>
@@ -39310,7 +39318,11 @@
           <t>9501894</t>
         </is>
       </c>
-      <c r="D696" t="inlineStr"/>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>DC-9501894/2026</t>
+        </is>
+      </c>
       <c r="E696" t="inlineStr">
         <is>
           <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
@@ -39418,7 +39430,11 @@
           <t>9518766</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>DC-9518766/2026</t>
+        </is>
+      </c>
       <c r="E698" t="inlineStr">
         <is>
           <t>MAIS CONSTRUTORA LTDA</t>
@@ -39528,7 +39544,7 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
+          <t>AMA-9502187/2026</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -39638,7 +39654,11 @@
           <t>9512044</t>
         </is>
       </c>
-      <c r="D702" t="inlineStr"/>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>DM-9512044/2026</t>
+        </is>
+      </c>
       <c r="E702" t="inlineStr">
         <is>
           <t>HWN ENGENHARIA LTDA</t>
@@ -39690,7 +39710,11 @@
           <t>9512043</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr"/>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
       <c r="E703" t="inlineStr">
         <is>
           <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
@@ -40022,7 +40046,11 @@
           <t>9500304</t>
         </is>
       </c>
-      <c r="D709" t="inlineStr"/>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
       <c r="E709" t="inlineStr">
         <is>
           <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>

--- a/upload/itens.xlsx
+++ b/upload/itens.xlsx
@@ -38092,7 +38092,7 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>DO-009482032/2025-L6</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -38706,11 +38706,7 @@
           <t>9511902</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr">
-        <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
+      <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr">
         <is>
           <t>LCM CONSTRUCAO E COMERCIO S.A</t>
@@ -38762,11 +38758,7 @@
           <t>9515457</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr">
-        <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
+      <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr">
         <is>
           <t>HWN ENGENHARIA LTDA</t>
@@ -38818,11 +38810,7 @@
           <t>9518140</t>
         </is>
       </c>
-      <c r="D687" t="inlineStr">
-        <is>
-          <t>DC-9518140/2026</t>
-        </is>
-      </c>
+      <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr">
         <is>
           <t>CONSTRUTORA SINARCO LTDA</t>
@@ -38930,11 +38918,7 @@
           <t>9518942</t>
         </is>
       </c>
-      <c r="D689" t="inlineStr">
-        <is>
-          <t>DC-9518942/2026</t>
-        </is>
-      </c>
+      <c r="D689" t="inlineStr"/>
       <c r="E689" t="inlineStr">
         <is>
           <t>CONSTRUTORA SINARCO LTDA</t>
@@ -38986,11 +38970,7 @@
           <t>9519017</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr">
-        <is>
-          <t>DC-9519017/2026</t>
-        </is>
-      </c>
+      <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr">
         <is>
           <t>BT CONSTRUCOES LTDA</t>
@@ -39042,11 +39022,7 @@
           <t>9519295</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr">
-        <is>
-          <t>DC-9519295/2026</t>
-        </is>
-      </c>
+      <c r="D691" t="inlineStr"/>
       <c r="E691" t="inlineStr">
         <is>
           <t>LCM CONSTRUCAO E COMERCIO S.A</t>
@@ -39098,11 +39074,7 @@
           <t>9519020</t>
         </is>
       </c>
-      <c r="D692" t="inlineStr">
-        <is>
-          <t>DC-9519020/2026</t>
-        </is>
-      </c>
+      <c r="D692" t="inlineStr"/>
       <c r="E692" t="inlineStr">
         <is>
           <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
@@ -39486,11 +39458,7 @@
           <t>9501894</t>
         </is>
       </c>
-      <c r="D699" t="inlineStr">
-        <is>
-          <t>DC-9501894/2026</t>
-        </is>
-      </c>
+      <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr">
         <is>
           <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
@@ -39598,11 +39566,7 @@
           <t>9518766</t>
         </is>
       </c>
-      <c r="D701" t="inlineStr">
-        <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
+      <c r="D701" t="inlineStr"/>
       <c r="E701" t="inlineStr">
         <is>
           <t>MAIS CONSTRUTORA LTDA</t>
@@ -39822,11 +39786,7 @@
           <t>9512044</t>
         </is>
       </c>
-      <c r="D705" t="inlineStr">
-        <is>
-          <t>DM-9512044/2026</t>
-        </is>
-      </c>
+      <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr">
         <is>
           <t>HWN ENGENHARIA LTDA</t>
@@ -39878,11 +39838,7 @@
           <t>9512043</t>
         </is>
       </c>
-      <c r="D706" t="inlineStr">
-        <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
+      <c r="D706" t="inlineStr"/>
       <c r="E706" t="inlineStr">
         <is>
           <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
@@ -40214,11 +40170,7 @@
           <t>9500304</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr">
-        <is>
-          <t>DM-9500304/2026</t>
-        </is>
-      </c>
+      <c r="D712" t="inlineStr"/>
       <c r="E712" t="inlineStr">
         <is>
           <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
@@ -40270,11 +40222,7 @@
           <t>9519034</t>
         </is>
       </c>
-      <c r="D713" t="inlineStr">
-        <is>
-          <t>DM-9519034/2026</t>
-        </is>
-      </c>
+      <c r="D713" t="inlineStr"/>
       <c r="E713" t="inlineStr">
         <is>
           <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>

--- a/upload/itens.xlsx
+++ b/upload/itens.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N732"/>
+  <dimension ref="A1:N734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32771,17 +32771,17 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>DM-008/2024</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -32807,13 +32807,13 @@
         <v>1</v>
       </c>
       <c r="L579" t="n">
-        <v>45388427.46</v>
+        <v>59075097</v>
       </c>
       <c r="M579" t="n">
-        <v>45388427.46</v>
+        <v>59075097</v>
       </c>
       <c r="N579" t="n">
-        <v>31307061.77</v>
+        <v>41801980.63</v>
       </c>
     </row>
     <row r="580">
@@ -32832,7 +32832,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DM-008/2024</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -32883,17 +32883,17 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>DM-009/2024</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -32919,13 +32919,13 @@
         <v>1</v>
       </c>
       <c r="L581" t="n">
-        <v>49516428.28</v>
+        <v>45388427.46</v>
       </c>
       <c r="M581" t="n">
-        <v>49516428.28</v>
+        <v>45388427.46</v>
       </c>
       <c r="N581" t="n">
-        <v>30648355.12</v>
+        <v>31307061.77</v>
       </c>
     </row>
     <row r="582">
@@ -32944,7 +32944,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-009/2024</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>DM-025/2023-A</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -33051,17 +33051,17 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>DM-012/2024</t>
+          <t>DM-025/2023-A</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ZAG LTDA</t>
+          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
         </is>
       </c>
       <c r="F584" t="n">
@@ -33087,13 +33087,13 @@
         <v>1</v>
       </c>
       <c r="L584" t="n">
-        <v>42427903.76</v>
+        <v>49516428.28</v>
       </c>
       <c r="M584" t="n">
-        <v>42427903.76</v>
+        <v>49516428.28</v>
       </c>
       <c r="N584" t="n">
-        <v>29715772.52</v>
+        <v>30648355.12</v>
       </c>
     </row>
     <row r="585">
@@ -33112,7 +33112,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DM-012/2024</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -33158,22 +33158,22 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>2301762 000039/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>9410180</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>DM-032/2023</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>CROS CONSTRUCOES S/A</t>
+          <t>CONSTRUTORA ZAG LTDA</t>
         </is>
       </c>
       <c r="F586" t="n">
@@ -33199,13 +33199,13 @@
         <v>1</v>
       </c>
       <c r="L586" t="n">
-        <v>51900209.21</v>
+        <v>42427903.76</v>
       </c>
       <c r="M586" t="n">
-        <v>51900209.21</v>
+        <v>42427903.76</v>
       </c>
       <c r="N586" t="n">
-        <v>43983527.2</v>
+        <v>29715772.52</v>
       </c>
     </row>
     <row r="587">
@@ -33214,22 +33214,22 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>2301762 000041/2023</t>
+          <t>2301762 000039/2023</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>9410175</t>
+          <t>9410180</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>DM-031/2023</t>
+          <t>DM-032/2023</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>CROS CONSTRUCOES S/A</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -33255,13 +33255,13 @@
         <v>1</v>
       </c>
       <c r="L587" t="n">
-        <v>17443062.11</v>
+        <v>51900209.21</v>
       </c>
       <c r="M587" t="n">
-        <v>17443062.11</v>
+        <v>51900209.21</v>
       </c>
       <c r="N587" t="n">
-        <v>16521453.91</v>
+        <v>43983527.2</v>
       </c>
     </row>
     <row r="588">
@@ -33270,22 +33270,22 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2301762 000045/2023</t>
+          <t>2301762 000041/2023</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>9424377</t>
+          <t>9410175</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>DM-019/2024</t>
+          <t>DM-031/2023</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>SINALMIG SINAIS E SISTEMAS LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -33308,16 +33308,16 @@
         </is>
       </c>
       <c r="K588" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L588" t="n">
-        <v>11996710.85</v>
+        <v>17443062.11</v>
       </c>
       <c r="M588" t="n">
-        <v>11996710.85</v>
+        <v>17443062.11</v>
       </c>
       <c r="N588" t="n">
-        <v>8049000</v>
+        <v>16521453.91</v>
       </c>
     </row>
     <row r="589">
@@ -33326,22 +33326,22 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>2301762 000046/2023</t>
+          <t>2301762 000045/2023</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>9413969</t>
+          <t>9424377</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>DM-004/2024</t>
+          <t>DM-019/2024</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
+          <t>SINALMIG SINAIS E SISTEMAS LTDA</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -33364,16 +33364,16 @@
         </is>
       </c>
       <c r="K589" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L589" t="n">
-        <v>1009319.98</v>
+        <v>11996710.85</v>
       </c>
       <c r="M589" t="n">
-        <v>1009319.98</v>
+        <v>11996710.85</v>
       </c>
       <c r="N589" t="n">
-        <v>948728.78</v>
+        <v>8049000</v>
       </c>
     </row>
     <row r="590">
@@ -33382,22 +33382,22 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>2301762 000048/2023</t>
+          <t>2301762 000046/2023</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>9412570</t>
+          <t>9413969</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>DM-003/2024</t>
+          <t>DM-004/2024</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -33423,13 +33423,13 @@
         <v>1</v>
       </c>
       <c r="L590" t="n">
-        <v>50023008.61</v>
+        <v>1009319.98</v>
       </c>
       <c r="M590" t="n">
-        <v>50023008.61</v>
+        <v>1009319.98</v>
       </c>
       <c r="N590" t="n">
-        <v>46770710.65</v>
+        <v>948728.78</v>
       </c>
     </row>
     <row r="591">
@@ -33438,22 +33438,22 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>2301762 000049/2023</t>
+          <t>2301762 000048/2023</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>9423384</t>
+          <t>9412570</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>DM-013/2024</t>
+          <t>DM-003/2024</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -33479,13 +33479,13 @@
         <v>1</v>
       </c>
       <c r="L591" t="n">
-        <v>78231455.95999999</v>
+        <v>50023008.61</v>
       </c>
       <c r="M591" t="n">
-        <v>78231455.95999999</v>
+        <v>50023008.61</v>
       </c>
       <c r="N591" t="n">
-        <v>67381496.97</v>
+        <v>46770710.65</v>
       </c>
     </row>
     <row r="592">
@@ -33494,22 +33494,22 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>2301762 000050/2023</t>
+          <t>2301762 000049/2023</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>9414641</t>
+          <t>9423384</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>DM-006/2024</t>
+          <t>DM-013/2024</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>E. B. O. - EMPRESA BRASILEIRA DE OBRAS LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -33535,13 +33535,13 @@
         <v>1</v>
       </c>
       <c r="L592" t="n">
-        <v>7567396.72</v>
+        <v>78231455.95999999</v>
       </c>
       <c r="M592" t="n">
-        <v>7567396.72</v>
+        <v>78231455.95999999</v>
       </c>
       <c r="N592" t="n">
-        <v>5949066.1</v>
+        <v>67381496.97</v>
       </c>
     </row>
     <row r="593">
@@ -33550,22 +33550,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000050/2023</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9414641</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>DM-014/2024</t>
+          <t>DM-006/2024</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>E. B. O. - EMPRESA BRASILEIRA DE OBRAS LTDA</t>
         </is>
       </c>
       <c r="F593" t="n">
@@ -33591,13 +33591,13 @@
         <v>1</v>
       </c>
       <c r="L593" t="n">
-        <v>57753580.93</v>
+        <v>7567396.72</v>
       </c>
       <c r="M593" t="n">
-        <v>57753580.93</v>
+        <v>7567396.72</v>
       </c>
       <c r="N593" t="n">
-        <v>37310856.76</v>
+        <v>5949066.1</v>
       </c>
     </row>
     <row r="594">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-014/2024</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -33667,17 +33667,17 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>DM-018/2024</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F595" t="n">
@@ -33703,13 +33703,13 @@
         <v>1</v>
       </c>
       <c r="L595" t="n">
-        <v>56623238.81</v>
+        <v>57753580.93</v>
       </c>
       <c r="M595" t="n">
-        <v>56623238.81</v>
+        <v>57753580.93</v>
       </c>
       <c r="N595" t="n">
-        <v>37153801.63</v>
+        <v>37310856.76</v>
       </c>
     </row>
     <row r="596">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DM-018/2024</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -33779,17 +33779,17 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>DM-016/2024</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="F597" t="n">
@@ -33815,13 +33815,13 @@
         <v>1</v>
       </c>
       <c r="L597" t="n">
-        <v>51505163.41</v>
+        <v>56623238.81</v>
       </c>
       <c r="M597" t="n">
-        <v>51505163.41</v>
+        <v>56623238.81</v>
       </c>
       <c r="N597" t="n">
-        <v>33479427.94</v>
+        <v>37153801.63</v>
       </c>
     </row>
     <row r="598">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-016/2024</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -33891,17 +33891,17 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>9424447</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>DM-015/2024</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -33927,13 +33927,13 @@
         <v>1</v>
       </c>
       <c r="L599" t="n">
-        <v>50334501.36</v>
+        <v>51505163.41</v>
       </c>
       <c r="M599" t="n">
-        <v>50334501.36</v>
+        <v>51505163.41</v>
       </c>
       <c r="N599" t="n">
-        <v>33230906.95</v>
+        <v>33479427.94</v>
       </c>
     </row>
     <row r="600">
@@ -33947,17 +33947,17 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9424447</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>DM-017/2024</t>
+          <t>DM-015/2024</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="F600" t="n">
@@ -33983,13 +33983,13 @@
         <v>1</v>
       </c>
       <c r="L600" t="n">
-        <v>50026623.29</v>
+        <v>50334501.36</v>
       </c>
       <c r="M600" t="n">
-        <v>50026623.29</v>
+        <v>50334501.36</v>
       </c>
       <c r="N600" t="n">
-        <v>32023158.45</v>
+        <v>33230906.95</v>
       </c>
     </row>
     <row r="601">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DM-017/2024</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -34059,17 +34059,17 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>DM-020/2024</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -34095,13 +34095,13 @@
         <v>1</v>
       </c>
       <c r="L602" t="n">
-        <v>57899353.16</v>
+        <v>50026623.29</v>
       </c>
       <c r="M602" t="n">
-        <v>57899353.16</v>
+        <v>50026623.29</v>
       </c>
       <c r="N602" t="n">
-        <v>34984519.25</v>
+        <v>32023158.45</v>
       </c>
     </row>
     <row r="603">
@@ -34120,7 +34120,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-020/2024</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -34171,17 +34171,17 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>DM-022/2024</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -34207,13 +34207,13 @@
         <v>1</v>
       </c>
       <c r="L604" t="n">
-        <v>61509573.94</v>
+        <v>57899353.16</v>
       </c>
       <c r="M604" t="n">
-        <v>61509573.94</v>
+        <v>57899353.16</v>
       </c>
       <c r="N604" t="n">
-        <v>42788655.89</v>
+        <v>34984519.25</v>
       </c>
     </row>
     <row r="605">
@@ -34232,7 +34232,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>DM-022/2024</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -34278,54 +34278,54 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>2301931 000001/2024</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>9440673</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>AEST-009440673/2024</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F606" t="n">
         <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>26883</v>
+        <v>1872</v>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I606" t="n">
-        <v>3502</v>
+        <v>5107</v>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K606" t="n">
         <v>1</v>
       </c>
       <c r="L606" t="n">
-        <v>7699669.8</v>
+        <v>61509573.94</v>
       </c>
       <c r="M606" t="n">
-        <v>7699669.8</v>
+        <v>61509573.94</v>
       </c>
       <c r="N606" t="n">
-        <v>5774752.44</v>
+        <v>42788655.89</v>
       </c>
     </row>
     <row r="607">
@@ -34344,7 +34344,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>AEST-009440673/2024</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -34390,22 +34390,22 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>2301931 000002/2024</t>
+          <t>2301931 000001/2024</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>9441233</t>
+          <t>9440673</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>AEST-9441233/2024</t>
+          <t>PO</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA E EXTENSAO UNIVERSITARIA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F608" t="n">
@@ -34431,13 +34431,13 @@
         <v>1</v>
       </c>
       <c r="L608" t="n">
-        <v>5947278.86</v>
+        <v>7699669.8</v>
       </c>
       <c r="M608" t="n">
-        <v>0</v>
+        <v>7699669.8</v>
       </c>
       <c r="N608" t="n">
-        <v>0</v>
+        <v>5774752.44</v>
       </c>
     </row>
     <row r="609">
@@ -34476,11 +34476,11 @@
         </is>
       </c>
       <c r="I609" t="n">
-        <v>3973</v>
+        <v>3502</v>
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K609" t="n">
@@ -34490,66 +34490,66 @@
         <v>5947278.86</v>
       </c>
       <c r="M609" t="n">
-        <v>5947278.86</v>
+        <v>0</v>
       </c>
       <c r="N609" t="n">
-        <v>5947278.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>1301017 000043/2024</t>
+          <t>2301931 000002/2024</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>9473911</t>
+          <t>9441233</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>9473911/2024</t>
+          <t>AEST-9441233/2024</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA E EXTENSAO UNIVERSITARIA</t>
         </is>
       </c>
       <c r="F610" t="n">
         <v>1</v>
       </c>
       <c r="G610" t="n">
-        <v>11207</v>
+        <v>26883</v>
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I610" t="n">
-        <v>3951</v>
+        <v>3973</v>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
         </is>
       </c>
       <c r="K610" t="n">
         <v>1</v>
       </c>
       <c r="L610" t="n">
-        <v>6941645.22</v>
+        <v>5947278.86</v>
       </c>
       <c r="M610" t="n">
-        <v>6941645.22</v>
+        <v>5947278.86</v>
       </c>
       <c r="N610" t="n">
-        <v>5206233.96</v>
+        <v>5947278.86</v>
       </c>
     </row>
     <row r="611">
@@ -34577,7 +34577,7 @@
         </is>
       </c>
       <c r="F611" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G611" t="n">
         <v>11207</v>
@@ -34602,10 +34602,10 @@
         <v>6941645.22</v>
       </c>
       <c r="M611" t="n">
-        <v>0</v>
+        <v>6941645.22</v>
       </c>
       <c r="N611" t="n">
-        <v>0</v>
+        <v>5206233.96</v>
       </c>
     </row>
     <row r="612">
@@ -34633,7 +34633,7 @@
         </is>
       </c>
       <c r="F612" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G612" t="n">
         <v>11207</v>
@@ -34670,54 +34670,54 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>1301606 000001/2025</t>
+          <t>1301017 000043/2024</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>9470224</t>
+          <t>9473911</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>DC-9470224/2025</t>
+          <t>9473911/2024</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>SENGE SERVICOS DE ENGENHARIA LTDA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="F613" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G613" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I613" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K613" t="n">
         <v>1</v>
       </c>
       <c r="L613" t="n">
-        <v>25933131.61</v>
+        <v>6941645.22</v>
       </c>
       <c r="M613" t="n">
-        <v>25933131.61</v>
+        <v>0</v>
       </c>
       <c r="N613" t="n">
-        <v>19446841.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
@@ -34726,22 +34726,22 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>2301520 000001/2025</t>
+          <t>1301606 000001/2025</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>9459022</t>
+          <t>9470224</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>DC-9459022/2025</t>
+          <t>DC-9470224/2025</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>SENGE SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F614" t="n">
@@ -34767,13 +34767,13 @@
         <v>1</v>
       </c>
       <c r="L614" t="n">
-        <v>13090078.19</v>
+        <v>25933131.61</v>
       </c>
       <c r="M614" t="n">
-        <v>13090078.19</v>
+        <v>25933131.61</v>
       </c>
       <c r="N614" t="n">
-        <v>9817558.640000001</v>
+        <v>19446841.31</v>
       </c>
     </row>
     <row r="615">
@@ -34787,12 +34787,12 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>9459023</t>
+          <t>9459022</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>DC-9459023/2025</t>
+          <t>DC-9459022/2025</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -34823,13 +34823,13 @@
         <v>1</v>
       </c>
       <c r="L615" t="n">
-        <v>39434905.89</v>
+        <v>13090078.19</v>
       </c>
       <c r="M615" t="n">
-        <v>39434905.89</v>
+        <v>13090078.19</v>
       </c>
       <c r="N615" t="n">
-        <v>29576179.41</v>
+        <v>9817558.640000001</v>
       </c>
     </row>
     <row r="616">
@@ -34838,54 +34838,54 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>2301520 000002/2025</t>
+          <t>2301520 000001/2025</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>9472756</t>
+          <t>9459023</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>DC-9472756/2025</t>
+          <t>DC-9459023/2025</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>ESTEL ENGENHARIA LTDA.</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F616" t="n">
         <v>1</v>
       </c>
       <c r="G616" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I616" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K616" t="n">
         <v>1</v>
       </c>
       <c r="L616" t="n">
-        <v>2332947.34</v>
+        <v>39434905.89</v>
       </c>
       <c r="M616" t="n">
-        <v>2332947.34</v>
+        <v>39434905.89</v>
       </c>
       <c r="N616" t="n">
-        <v>1655673.22</v>
+        <v>29576179.41</v>
       </c>
     </row>
     <row r="617">
@@ -34904,7 +34904,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>DM-001/2022</t>
+          <t>DC-9472756/2025</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -34950,54 +34950,54 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2301520 000004/2025</t>
+          <t>2301520 000002/2025</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>9459021</t>
+          <t>9472756</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>DC-9459021/2025</t>
+          <t>DM-001/2022</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>ESTEL ENGENHARIA LTDA.</t>
         </is>
       </c>
       <c r="F618" t="n">
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I618" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K618" t="n">
         <v>1</v>
       </c>
       <c r="L618" t="n">
-        <v>40411563.13</v>
+        <v>2332947.34</v>
       </c>
       <c r="M618" t="n">
-        <v>40411563.13</v>
+        <v>2332947.34</v>
       </c>
       <c r="N618" t="n">
-        <v>35900000</v>
+        <v>1655673.22</v>
       </c>
     </row>
     <row r="619">
@@ -35006,22 +35006,22 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>2301520 000007/2025</t>
+          <t>2301520 000004/2025</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>9468321</t>
+          <t>9459021</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>DC-9468321/2025</t>
+          <t>DC-9459021/2025</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>G S COSTA CONSTRUTORA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F619" t="n">
@@ -35047,13 +35047,13 @@
         <v>1</v>
       </c>
       <c r="L619" t="n">
-        <v>2445446.33</v>
+        <v>40411563.13</v>
       </c>
       <c r="M619" t="n">
-        <v>2445446.33</v>
+        <v>40411563.13</v>
       </c>
       <c r="N619" t="n">
-        <v>2380000</v>
+        <v>35900000</v>
       </c>
     </row>
     <row r="620">
@@ -35062,54 +35062,54 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>2301520 000008/2025</t>
+          <t>2301520 000007/2025</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>9472752</t>
+          <t>9468321</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>DC-9472752/2025</t>
+          <t>DC-9468321/2025</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>G S COSTA CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="F620" t="n">
         <v>1</v>
       </c>
       <c r="G620" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I620" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K620" t="n">
         <v>1</v>
       </c>
       <c r="L620" t="n">
-        <v>9357672.390000001</v>
+        <v>2445446.33</v>
       </c>
       <c r="M620" t="n">
-        <v>9357672.390000001</v>
+        <v>2445446.33</v>
       </c>
       <c r="N620" t="n">
-        <v>7056321.74</v>
+        <v>2380000</v>
       </c>
     </row>
     <row r="621">
@@ -35128,7 +35128,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>DM-001/2021</t>
+          <t>DC-9472752/2025</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
@@ -35174,54 +35174,54 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>2301520 000010/2025</t>
+          <t>2301520 000008/2025</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>9473951</t>
+          <t>9472752</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>DC-9473951/2025</t>
+          <t>DM-001/2021</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F622" t="n">
         <v>1</v>
       </c>
       <c r="G622" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I622" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K622" t="n">
         <v>1</v>
       </c>
       <c r="L622" t="n">
-        <v>63771944.67</v>
+        <v>9357672.390000001</v>
       </c>
       <c r="M622" t="n">
-        <v>63771944.67</v>
+        <v>9357672.390000001</v>
       </c>
       <c r="N622" t="n">
-        <v>45918998.95</v>
+        <v>7056321.74</v>
       </c>
     </row>
     <row r="623">
@@ -35230,22 +35230,22 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>2301520 000011/2025</t>
+          <t>2301520 000010/2025</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>9471605</t>
+          <t>9473951</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>DC-9471605/2025</t>
+          <t>DC-9473951/2025</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="F623" t="n">
@@ -35271,13 +35271,13 @@
         <v>1</v>
       </c>
       <c r="L623" t="n">
-        <v>9523161.51</v>
+        <v>63771944.67</v>
       </c>
       <c r="M623" t="n">
-        <v>9523161.51</v>
+        <v>63771944.67</v>
       </c>
       <c r="N623" t="n">
-        <v>9522992.289999999</v>
+        <v>45918998.95</v>
       </c>
     </row>
     <row r="624">
@@ -35286,22 +35286,22 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2301520 000016/2025</t>
+          <t>2301520 000011/2025</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>9473175</t>
+          <t>9471605</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>DC-009473175/2025</t>
+          <t>DC-9471605/2025</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>CONSTRUTORA A GASPAR S/A</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="F624" t="n">
@@ -35327,13 +35327,13 @@
         <v>1</v>
       </c>
       <c r="L624" t="n">
-        <v>252967153.57</v>
+        <v>9523161.51</v>
       </c>
       <c r="M624" t="n">
-        <v>252967153.57</v>
+        <v>9523161.51</v>
       </c>
       <c r="N624" t="n">
-        <v>207490000</v>
+        <v>9522992.289999999</v>
       </c>
     </row>
     <row r="625">
@@ -35352,7 +35352,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>DC-012/2023</t>
+          <t>DC-009473175/2025</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -35398,22 +35398,22 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2301520 000018/2025</t>
+          <t>2301520 000016/2025</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>9473949</t>
+          <t>9473175</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>DC-9473949/2025</t>
+          <t>DC-012/2023</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>CONSTRUTORA A GASPAR S/A</t>
         </is>
       </c>
       <c r="F626" t="n">
@@ -35439,13 +35439,13 @@
         <v>1</v>
       </c>
       <c r="L626" t="n">
-        <v>7210196.37</v>
+        <v>252967153.57</v>
       </c>
       <c r="M626" t="n">
-        <v>7210196.37</v>
+        <v>252967153.57</v>
       </c>
       <c r="N626" t="n">
-        <v>5978999.99</v>
+        <v>207490000</v>
       </c>
     </row>
     <row r="627">
@@ -35454,22 +35454,22 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>2301520 000019/2024</t>
+          <t>2301520 000018/2025</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>9447760</t>
+          <t>9473949</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>DC-9447760/2025</t>
+          <t>DC-9473949/2025</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="F627" t="n">
@@ -35495,13 +35495,13 @@
         <v>1</v>
       </c>
       <c r="L627" t="n">
-        <v>9049369.99</v>
+        <v>7210196.37</v>
       </c>
       <c r="M627" t="n">
-        <v>9049369.99</v>
+        <v>7210196.37</v>
       </c>
       <c r="N627" t="n">
-        <v>8415499.810000001</v>
+        <v>5978999.99</v>
       </c>
     </row>
     <row r="628">
@@ -35515,12 +35515,12 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>9447761</t>
+          <t>9447760</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>DC-9447761/2025</t>
+          <t>DC-9447760/2025</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -35551,13 +35551,13 @@
         <v>1</v>
       </c>
       <c r="L628" t="n">
-        <v>5032564.85</v>
+        <v>9049369.99</v>
       </c>
       <c r="M628" t="n">
-        <v>5032564.85</v>
+        <v>9049369.99</v>
       </c>
       <c r="N628" t="n">
-        <v>4776981.58</v>
+        <v>8415499.810000001</v>
       </c>
     </row>
     <row r="629">
@@ -35566,54 +35566,54 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>2301520 000022/2025</t>
+          <t>2301520 000019/2024</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>9492718</t>
+          <t>9447761</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>DC-9492718/2025</t>
+          <t>DC-9447761/2025</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F629" t="n">
         <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I629" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K629" t="n">
         <v>1</v>
       </c>
       <c r="L629" t="n">
-        <v>4575396.26</v>
+        <v>5032564.85</v>
       </c>
       <c r="M629" t="n">
-        <v>4575396.26</v>
+        <v>5032564.85</v>
       </c>
       <c r="N629" t="n">
-        <v>3187539.16</v>
+        <v>4776981.58</v>
       </c>
     </row>
     <row r="630">
@@ -35622,17 +35622,17 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>2301520 000023/2025</t>
+          <t>2301520 000022/2025</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>9492065</t>
+          <t>9492718</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>DC-9492065/2025</t>
+          <t>DC-9492718/2025</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -35663,13 +35663,13 @@
         <v>1</v>
       </c>
       <c r="L630" t="n">
-        <v>3499878.79</v>
+        <v>4575396.26</v>
       </c>
       <c r="M630" t="n">
-        <v>3499878.79</v>
+        <v>4575396.26</v>
       </c>
       <c r="N630" t="n">
-        <v>2624909.09</v>
+        <v>3187539.16</v>
       </c>
     </row>
     <row r="631">
@@ -35678,54 +35678,54 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>2301520 000024/2024</t>
+          <t>2301520 000023/2025</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>9458476</t>
+          <t>9492065</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>DC-9458476/2025</t>
+          <t>DC-9492065/2025</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
         </is>
       </c>
       <c r="F631" t="n">
         <v>1</v>
       </c>
       <c r="G631" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I631" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K631" t="n">
         <v>1</v>
       </c>
       <c r="L631" t="n">
-        <v>104863231.67</v>
+        <v>3499878.79</v>
       </c>
       <c r="M631" t="n">
-        <v>104863231.67</v>
+        <v>3499878.79</v>
       </c>
       <c r="N631" t="n">
-        <v>78647423.75</v>
+        <v>2624909.09</v>
       </c>
     </row>
     <row r="632">
@@ -35734,54 +35734,54 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>2301520 000024/2025</t>
+          <t>2301520 000024/2024</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>9491012</t>
+          <t>9458476</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>DC-9491012/2025</t>
+          <t>DC-9458476/2025</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F632" t="n">
         <v>1</v>
       </c>
       <c r="G632" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I632" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K632" t="n">
         <v>1</v>
       </c>
       <c r="L632" t="n">
-        <v>5765714.24</v>
+        <v>104863231.67</v>
       </c>
       <c r="M632" t="n">
-        <v>5765714.24</v>
+        <v>104863231.67</v>
       </c>
       <c r="N632" t="n">
-        <v>4324285.68</v>
+        <v>78647423.75</v>
       </c>
     </row>
     <row r="633">
@@ -35790,54 +35790,54 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>2301520 000025/2024</t>
+          <t>2301520 000024/2025</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>9448965</t>
+          <t>9491012</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>DC-9448965/2025</t>
+          <t>DC-9491012/2025</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>CONSTRUTORA MARINS LTDA</t>
+          <t>PRODEC CONSULTORIA PARA DECISAO SOCIEDADE SIMPLES LTDA.</t>
         </is>
       </c>
       <c r="F633" t="n">
         <v>1</v>
       </c>
       <c r="G633" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I633" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K633" t="n">
         <v>1</v>
       </c>
       <c r="L633" t="n">
-        <v>4553972.46</v>
+        <v>5765714.24</v>
       </c>
       <c r="M633" t="n">
-        <v>4553972.46</v>
+        <v>5765714.24</v>
       </c>
       <c r="N633" t="n">
-        <v>4553800</v>
+        <v>4324285.68</v>
       </c>
     </row>
     <row r="634">
@@ -35846,54 +35846,54 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>2301520 000027/2023</t>
+          <t>2301520 000025/2024</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9448965</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>DC-9453556/2025</t>
+          <t>DC-9448965/2025</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>PROJEL - ENGENHARIA ESPECIALIZADA LTDA</t>
+          <t>CONSTRUTORA MARINS LTDA</t>
         </is>
       </c>
       <c r="F634" t="n">
         <v>1</v>
       </c>
       <c r="G634" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I634" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K634" t="n">
         <v>1</v>
       </c>
       <c r="L634" t="n">
-        <v>10169679.88</v>
+        <v>4553972.46</v>
       </c>
       <c r="M634" t="n">
-        <v>10169679.88</v>
+        <v>4553972.46</v>
       </c>
       <c r="N634" t="n">
-        <v>9659997.08</v>
+        <v>4553800</v>
       </c>
     </row>
     <row r="635">
@@ -35912,7 +35912,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9453556/2025</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -35958,54 +35958,54 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>2301520 000027/2024</t>
+          <t>2301520 000027/2023</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>9458861</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>DC-9458861/2025</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>BT CONSTRUCOES LTDA</t>
+          <t>PROJEL - ENGENHARIA ESPECIALIZADA LTDA</t>
         </is>
       </c>
       <c r="F636" t="n">
         <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I636" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K636" t="n">
         <v>1</v>
       </c>
       <c r="L636" t="n">
-        <v>32377230.57</v>
+        <v>10169679.88</v>
       </c>
       <c r="M636" t="n">
-        <v>32377230.57</v>
+        <v>10169679.88</v>
       </c>
       <c r="N636" t="n">
-        <v>24981452.5</v>
+        <v>9659997.08</v>
       </c>
     </row>
     <row r="637">
@@ -36014,22 +36014,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>2301520 000028/2025</t>
+          <t>2301520 000027/2024</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>9491013</t>
+          <t>9458861</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>DC-9491013/2025</t>
+          <t>DC-9458861/2025</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>VEREDA ENGENHARIA LTDA</t>
+          <t>BT CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F637" t="n">
@@ -36055,13 +36055,13 @@
         <v>1</v>
       </c>
       <c r="L637" t="n">
-        <v>22364155.09</v>
+        <v>32377230.57</v>
       </c>
       <c r="M637" t="n">
-        <v>22364155.09</v>
+        <v>32377230.57</v>
       </c>
       <c r="N637" t="n">
-        <v>20125000</v>
+        <v>24981452.5</v>
       </c>
     </row>
     <row r="638">
@@ -36070,22 +36070,22 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>2301520 000029/2025</t>
+          <t>2301520 000028/2025</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>9478759</t>
+          <t>9491013</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>DC-9478759/2025</t>
+          <t>DC-9491013/2025</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>SOCIEDADE GERAL DE EMPREITADAS LIMITADA -</t>
+          <t>VEREDA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F638" t="n">
@@ -36111,13 +36111,13 @@
         <v>1</v>
       </c>
       <c r="L638" t="n">
-        <v>17183580.33</v>
+        <v>22364155.09</v>
       </c>
       <c r="M638" t="n">
-        <v>17183580.33</v>
+        <v>22364155.09</v>
       </c>
       <c r="N638" t="n">
-        <v>14619000</v>
+        <v>20125000</v>
       </c>
     </row>
     <row r="639">
@@ -36126,54 +36126,54 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>2301520 000031/2025</t>
+          <t>2301520 000029/2025</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>9481581</t>
+          <t>9478759</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>DC-9481581/2025</t>
+          <t>DC-9478759/2025</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
+          <t>SOCIEDADE GERAL DE EMPREITADAS LIMITADA -</t>
         </is>
       </c>
       <c r="F639" t="n">
         <v>1</v>
       </c>
       <c r="G639" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I639" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K639" t="n">
         <v>1</v>
       </c>
       <c r="L639" t="n">
-        <v>29147315.1</v>
+        <v>17183580.33</v>
       </c>
       <c r="M639" t="n">
-        <v>29147315.1</v>
+        <v>17183580.33</v>
       </c>
       <c r="N639" t="n">
-        <v>21860486.4</v>
+        <v>14619000</v>
       </c>
     </row>
     <row r="640">
@@ -36201,7 +36201,7 @@
         </is>
       </c>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G640" t="n">
         <v>10774</v>
@@ -36226,10 +36226,10 @@
         <v>29147315.1</v>
       </c>
       <c r="M640" t="n">
-        <v>0</v>
+        <v>29147315.1</v>
       </c>
       <c r="N640" t="n">
-        <v>0</v>
+        <v>21860486.4</v>
       </c>
     </row>
     <row r="641">
@@ -36238,54 +36238,54 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>2301520 000032/2025</t>
+          <t>2301520 000031/2025</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>9479677</t>
+          <t>9481581</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>DC-9479677/2025</t>
+          <t>DC-9481581/2025</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>CROS CONSTRUCOES S/A</t>
+          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
         </is>
       </c>
       <c r="F641" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G641" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I641" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K641" t="n">
         <v>1</v>
       </c>
       <c r="L641" t="n">
-        <v>65309420.72</v>
+        <v>29147315.1</v>
       </c>
       <c r="M641" t="n">
-        <v>65309420.72</v>
+        <v>0</v>
       </c>
       <c r="N641" t="n">
-        <v>57467603.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="642">
@@ -36294,22 +36294,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>2301520 000038/2025</t>
+          <t>2301520 000032/2025</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>9492083</t>
+          <t>9479677</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>DC-9492083/2025</t>
+          <t>DC-9479677/2025</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>CROS CONSTRUCOES S/A</t>
         </is>
       </c>
       <c r="F642" t="n">
@@ -36335,13 +36335,13 @@
         <v>1</v>
       </c>
       <c r="L642" t="n">
-        <v>74235570.89</v>
+        <v>65309420.72</v>
       </c>
       <c r="M642" t="n">
-        <v>74235570.89</v>
+        <v>65309420.72</v>
       </c>
       <c r="N642" t="n">
-        <v>59890000</v>
+        <v>57467603.75</v>
       </c>
     </row>
     <row r="643">
@@ -36350,54 +36350,54 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>2301601 000002/2025</t>
+          <t>2301520 000038/2025</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>9470883</t>
+          <t>9492083</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>DPEI-9470883</t>
+          <t>DC-9492083/2025</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>DYNATEST ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F643" t="n">
         <v>1</v>
       </c>
       <c r="G643" t="n">
-        <v>10693</v>
+        <v>1740</v>
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS DE ENGENHARIA.</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I643" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K643" t="n">
         <v>1</v>
       </c>
       <c r="L643" t="n">
-        <v>34605227.68</v>
+        <v>74235570.89</v>
       </c>
       <c r="M643" t="n">
-        <v>34605227.68</v>
+        <v>74235570.89</v>
       </c>
       <c r="N643" t="n">
-        <v>25953920.64</v>
+        <v>59890000</v>
       </c>
     </row>
     <row r="644">
@@ -36406,33 +36406,33 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>2301601 000003/2025</t>
+          <t>2301601 000002/2025</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>9470151</t>
+          <t>9470883</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>DPEI-9470151</t>
+          <t>DPEI-9470883</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>DYNATEST ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F644" t="n">
         <v>1</v>
       </c>
       <c r="G644" t="n">
-        <v>46850</v>
+        <v>10693</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>SERVICO GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS DEENGENHARIA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS DE ENGENHARIA.</t>
         </is>
       </c>
       <c r="I644" t="n">
@@ -36447,13 +36447,13 @@
         <v>1</v>
       </c>
       <c r="L644" t="n">
-        <v>28087551.11</v>
+        <v>34605227.68</v>
       </c>
       <c r="M644" t="n">
-        <v>28087551.11</v>
+        <v>34605227.68</v>
       </c>
       <c r="N644" t="n">
-        <v>22458906.7</v>
+        <v>25953920.64</v>
       </c>
     </row>
     <row r="645">
@@ -36462,54 +36462,54 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>2301601 000004/2024</t>
+          <t>2301601 000003/2025</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>9447985</t>
+          <t>9470151</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>DPEI-9447985</t>
+          <t>DPEI-9470151</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>HOUER ENGENHARIA LTDA</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F645" t="n">
         <v>1</v>
       </c>
       <c r="G645" t="n">
-        <v>23159</v>
+        <v>46850</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICO GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS DEENGENHARIA</t>
         </is>
       </c>
       <c r="I645" t="n">
-        <v>3981</v>
+        <v>3951</v>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K645" t="n">
         <v>1</v>
       </c>
       <c r="L645" t="n">
-        <v>6361273.94</v>
+        <v>28087551.11</v>
       </c>
       <c r="M645" t="n">
-        <v>6361273.94</v>
+        <v>28087551.11</v>
       </c>
       <c r="N645" t="n">
-        <v>2540551.02</v>
+        <v>22458906.7</v>
       </c>
     </row>
     <row r="646">
@@ -36518,50 +36518,54 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>2301601 000004/2025</t>
+          <t>2301601 000004/2024</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>9478110</t>
-        </is>
-      </c>
-      <c r="D646" t="inlineStr"/>
+          <t>9447985</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>DPEI-9447985</t>
+        </is>
+      </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>FUNDACAO GETULIO VARGAS</t>
+          <t>HOUER ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F646" t="n">
         <v>1</v>
       </c>
       <c r="G646" t="n">
-        <v>26883</v>
+        <v>23159</v>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I646" t="n">
-        <v>3502</v>
+        <v>3981</v>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K646" t="n">
         <v>1</v>
       </c>
       <c r="L646" t="n">
-        <v>22278613.12</v>
+        <v>6361273.94</v>
       </c>
       <c r="M646" t="n">
-        <v>22278613.12</v>
+        <v>6361273.94</v>
       </c>
       <c r="N646" t="n">
-        <v>22278613.12</v>
+        <v>2540551.02</v>
       </c>
     </row>
     <row r="647">
@@ -36570,22 +36574,18 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>2301601 000005/2025</t>
+          <t>2301601 000004/2025</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>9478941</t>
-        </is>
-      </c>
-      <c r="D647" t="inlineStr">
-        <is>
-          <t>DPEI-9478941/2025</t>
-        </is>
-      </c>
+          <t>9478110</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr"/>
       <c r="E647" t="inlineStr">
         <is>
-          <t>FUNDACAO CHRISTIANO OTTONI</t>
+          <t>FUNDACAO GETULIO VARGAS</t>
         </is>
       </c>
       <c r="F647" t="n">
@@ -36611,13 +36611,13 @@
         <v>1</v>
       </c>
       <c r="L647" t="n">
-        <v>2401689.3</v>
+        <v>22278613.12</v>
       </c>
       <c r="M647" t="n">
-        <v>2401689.3</v>
+        <v>22278613.12</v>
       </c>
       <c r="N647" t="n">
-        <v>2401689.3</v>
+        <v>22278613.12</v>
       </c>
     </row>
     <row r="648">
@@ -36626,54 +36626,54 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>2301617 000002/2025</t>
+          <t>2301601 000005/2025</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>9461425</t>
+          <t>9478941</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>AMA-9461425/2025</t>
+          <t>DPEI-9478941/2025</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
+          <t>FUNDACAO CHRISTIANO OTTONI</t>
         </is>
       </c>
       <c r="F648" t="n">
         <v>1</v>
       </c>
       <c r="G648" t="n">
-        <v>23167</v>
+        <v>26883</v>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I648" t="n">
-        <v>3999</v>
+        <v>3502</v>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K648" t="n">
         <v>1</v>
       </c>
       <c r="L648" t="n">
-        <v>31713.27</v>
+        <v>2401689.3</v>
       </c>
       <c r="M648" t="n">
-        <v>31713.27</v>
+        <v>2401689.3</v>
       </c>
       <c r="N648" t="n">
-        <v>31713.27</v>
+        <v>2401689.3</v>
       </c>
     </row>
     <row r="649">
@@ -36723,13 +36723,13 @@
         <v>1</v>
       </c>
       <c r="L649" t="n">
-        <v>38863.58</v>
+        <v>31713.27</v>
       </c>
       <c r="M649" t="n">
-        <v>38863.58</v>
+        <v>31713.27</v>
       </c>
       <c r="N649" t="n">
-        <v>38863.58</v>
+        <v>31713.27</v>
       </c>
     </row>
     <row r="650">
@@ -36738,22 +36738,22 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>2301617 000004/2024</t>
+          <t>2301617 000002/2025</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>9447965</t>
+          <t>9461425</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>AMA-9447965/2025</t>
+          <t>AMA-9461425/2025</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>DIRECAO CONSULTORIA E ENGENHARIA LTDA</t>
+          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
         </is>
       </c>
       <c r="F650" t="n">
@@ -36779,13 +36779,13 @@
         <v>1</v>
       </c>
       <c r="L650" t="n">
-        <v>965839.63</v>
+        <v>38863.58</v>
       </c>
       <c r="M650" t="n">
-        <v>965839.63</v>
+        <v>38863.58</v>
       </c>
       <c r="N650" t="n">
-        <v>924684.42</v>
+        <v>38863.58</v>
       </c>
     </row>
     <row r="651">
@@ -36794,17 +36794,17 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>2301617 000005/2024</t>
+          <t>2301617 000004/2024</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>9458828</t>
+          <t>9447965</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>AMA-9458828/2025</t>
+          <t>AMA-9447965/2025</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -36835,13 +36835,13 @@
         <v>1</v>
       </c>
       <c r="L651" t="n">
-        <v>839153.24</v>
+        <v>965839.63</v>
       </c>
       <c r="M651" t="n">
-        <v>839153.24</v>
+        <v>965839.63</v>
       </c>
       <c r="N651" t="n">
-        <v>803371.39</v>
+        <v>924684.42</v>
       </c>
     </row>
     <row r="652">
@@ -36850,54 +36850,54 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301617 000005/2024</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>9471830</t>
+          <t>9458828</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>DM-9471830/2025</t>
+          <t>AMA-9458828/2025</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>DIRECAO CONSULTORIA E ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F652" t="n">
         <v>1</v>
       </c>
       <c r="G652" t="n">
-        <v>1872</v>
+        <v>23167</v>
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
         </is>
       </c>
       <c r="I652" t="n">
-        <v>5107</v>
+        <v>3999</v>
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K652" t="n">
         <v>1</v>
       </c>
       <c r="L652" t="n">
-        <v>75462448.56</v>
+        <v>839153.24</v>
       </c>
       <c r="M652" t="n">
-        <v>75462448.56</v>
+        <v>839153.24</v>
       </c>
       <c r="N652" t="n">
-        <v>53573999.99</v>
+        <v>803371.39</v>
       </c>
     </row>
     <row r="653">
@@ -36911,17 +36911,17 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>9471832</t>
+          <t>9471830</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>DM-9471832/2025</t>
+          <t>DM-9471830/2025</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F653" t="n">
@@ -36947,13 +36947,13 @@
         <v>1</v>
       </c>
       <c r="L653" t="n">
-        <v>74549476.59</v>
+        <v>75462448.56</v>
       </c>
       <c r="M653" t="n">
-        <v>74549476.59</v>
+        <v>75462448.56</v>
       </c>
       <c r="N653" t="n">
-        <v>49093539.45</v>
+        <v>53573999.99</v>
       </c>
     </row>
     <row r="654">
@@ -36967,17 +36967,17 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>9471834</t>
+          <t>9471832</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>DM-9471834/2025</t>
+          <t>DM-9471832/2025</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F654" t="n">
@@ -37003,13 +37003,13 @@
         <v>1</v>
       </c>
       <c r="L654" t="n">
-        <v>71047185.15000001</v>
+        <v>74549476.59</v>
       </c>
       <c r="M654" t="n">
-        <v>71047185.15000001</v>
+        <v>74549476.59</v>
       </c>
       <c r="N654" t="n">
-        <v>50960749.38</v>
+        <v>49093539.45</v>
       </c>
     </row>
     <row r="655">
@@ -37023,17 +37023,17 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>9471835</t>
+          <t>9471834</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>DM-9471835/2025</t>
+          <t>DM-9471834/2025</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
         </is>
       </c>
       <c r="F655" t="n">
@@ -37059,13 +37059,13 @@
         <v>1</v>
       </c>
       <c r="L655" t="n">
-        <v>71318172.81999999</v>
+        <v>71047185.15000001</v>
       </c>
       <c r="M655" t="n">
-        <v>71318172.81999999</v>
+        <v>71047185.15000001</v>
       </c>
       <c r="N655" t="n">
-        <v>44573000</v>
+        <v>50960749.38</v>
       </c>
     </row>
     <row r="656">
@@ -37079,17 +37079,17 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>9471879</t>
+          <t>9471835</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>DM-9471879/2025</t>
+          <t>DM-9471835/2025</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>MA ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F656" t="n">
@@ -37115,13 +37115,13 @@
         <v>1</v>
       </c>
       <c r="L656" t="n">
-        <v>80365266.31999999</v>
+        <v>71318172.81999999</v>
       </c>
       <c r="M656" t="n">
-        <v>80365266.31999999</v>
+        <v>71318172.81999999</v>
       </c>
       <c r="N656" t="n">
-        <v>53241874.38</v>
+        <v>44573000</v>
       </c>
     </row>
     <row r="657">
@@ -37135,17 +37135,17 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>9471880</t>
+          <t>9471879</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>DM-9471880/2025</t>
+          <t>DM-9471879/2025</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>MA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F657" t="n">
@@ -37171,13 +37171,13 @@
         <v>1</v>
       </c>
       <c r="L657" t="n">
-        <v>76047809.47</v>
+        <v>80365266.31999999</v>
       </c>
       <c r="M657" t="n">
-        <v>76047809.47</v>
+        <v>80365266.31999999</v>
       </c>
       <c r="N657" t="n">
-        <v>51814575.44</v>
+        <v>53241874.38</v>
       </c>
     </row>
     <row r="658">
@@ -37191,17 +37191,17 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>9471881</t>
+          <t>9471880</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>DM-9471881/2025</t>
+          <t>DM-9471880/2025</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CTC LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F658" t="n">
@@ -37227,13 +37227,13 @@
         <v>1</v>
       </c>
       <c r="L658" t="n">
-        <v>76234321.51000001</v>
+        <v>76047809.47</v>
       </c>
       <c r="M658" t="n">
-        <v>76234321.51000001</v>
+        <v>76047809.47</v>
       </c>
       <c r="N658" t="n">
-        <v>53358800</v>
+        <v>51814575.44</v>
       </c>
     </row>
     <row r="659">
@@ -37247,17 +37247,17 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>9473163</t>
+          <t>9471881</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>DM-9473163/2025</t>
+          <t>DM-9471881/2025</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>GUAXIMA ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CTC LTDA</t>
         </is>
       </c>
       <c r="F659" t="n">
@@ -37283,13 +37283,13 @@
         <v>1</v>
       </c>
       <c r="L659" t="n">
-        <v>88896704.79000001</v>
+        <v>76234321.51000001</v>
       </c>
       <c r="M659" t="n">
-        <v>88896704.79000001</v>
+        <v>76234321.51000001</v>
       </c>
       <c r="N659" t="n">
-        <v>59299394.97</v>
+        <v>53358800</v>
       </c>
     </row>
     <row r="660">
@@ -37298,22 +37298,22 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>2301762 000004/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>9473312</t>
+          <t>9473163</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>DM-9473312/2025</t>
+          <t>DM-9473163/2025</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>MATRIX INFRAESTRUTURA LTDA - 'EM RECUPERACAO JUDICIAL'</t>
+          <t>GUAXIMA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F660" t="n">
@@ -37339,13 +37339,13 @@
         <v>1</v>
       </c>
       <c r="L660" t="n">
-        <v>8322333.63</v>
+        <v>88896704.79000001</v>
       </c>
       <c r="M660" t="n">
-        <v>8322333.63</v>
+        <v>88896704.79000001</v>
       </c>
       <c r="N660" t="n">
-        <v>7074995.71</v>
+        <v>59299394.97</v>
       </c>
     </row>
     <row r="661">
@@ -37354,17 +37354,17 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>2301762 000005/2025</t>
+          <t>2301762 000004/2025</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>9474704</t>
+          <t>9473312</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>DM-9474704/2025</t>
+          <t>DM-9473312/2025</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -37395,13 +37395,13 @@
         <v>1</v>
       </c>
       <c r="L661" t="n">
-        <v>9663464.630000001</v>
+        <v>8322333.63</v>
       </c>
       <c r="M661" t="n">
-        <v>9663464.630000001</v>
+        <v>8322333.63</v>
       </c>
       <c r="N661" t="n">
-        <v>7710000</v>
+        <v>7074995.71</v>
       </c>
     </row>
     <row r="662">
@@ -37410,22 +37410,22 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>2301762 000016/2025</t>
+          <t>2301762 000005/2025</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>9485592</t>
+          <t>9474704</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>DM-9485592/2025</t>
+          <t>DM-9474704/2025</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>MATRIX INFRAESTRUTURA LTDA - 'EM RECUPERACAO JUDICIAL'</t>
         </is>
       </c>
       <c r="F662" t="n">
@@ -37451,13 +37451,13 @@
         <v>1</v>
       </c>
       <c r="L662" t="n">
-        <v>13962359.26</v>
+        <v>9663464.630000001</v>
       </c>
       <c r="M662" t="n">
-        <v>13962359.26</v>
+        <v>9663464.630000001</v>
       </c>
       <c r="N662" t="n">
-        <v>10929975.56</v>
+        <v>7710000</v>
       </c>
     </row>
     <row r="663">
@@ -37466,22 +37466,22 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>2301762 000017/2024</t>
+          <t>2301762 000016/2025</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>9447456</t>
+          <t>9485592</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>DM-9447456/2024</t>
+          <t>DM-9485592/2025</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F663" t="n">
@@ -37507,13 +37507,13 @@
         <v>1</v>
       </c>
       <c r="L663" t="n">
-        <v>6557067.25</v>
+        <v>13962359.26</v>
       </c>
       <c r="M663" t="n">
-        <v>6557067.25</v>
+        <v>13962359.26</v>
       </c>
       <c r="N663" t="n">
-        <v>4917800.43</v>
+        <v>10929975.56</v>
       </c>
     </row>
     <row r="664">
@@ -37522,22 +37522,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>2301762 000017/2025</t>
+          <t>2301762 000017/2024</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>9485591</t>
+          <t>9447456</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>DM-9485591/2025</t>
+          <t>DM-9447456/2024</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F664" t="n">
@@ -37563,13 +37563,13 @@
         <v>1</v>
       </c>
       <c r="L664" t="n">
-        <v>8331047.13</v>
+        <v>6557067.25</v>
       </c>
       <c r="M664" t="n">
-        <v>8331047.13</v>
+        <v>6557067.25</v>
       </c>
       <c r="N664" t="n">
-        <v>6199729.76</v>
+        <v>4917800.43</v>
       </c>
     </row>
     <row r="665">
@@ -37578,22 +37578,22 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>2301762 000018/2024</t>
+          <t>2301762 000017/2025</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>9454417</t>
+          <t>9485591</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>DM-9454417/2025</t>
+          <t>DM-9485591/2025</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F665" t="n">
@@ -37619,13 +37619,13 @@
         <v>1</v>
       </c>
       <c r="L665" t="n">
-        <v>38329183.15</v>
+        <v>8331047.13</v>
       </c>
       <c r="M665" t="n">
-        <v>38329183.15</v>
+        <v>8331047.13</v>
       </c>
       <c r="N665" t="n">
-        <v>28746887.36</v>
+        <v>6199729.76</v>
       </c>
     </row>
     <row r="666">
@@ -37634,22 +37634,22 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>2301762 000019/2024</t>
+          <t>2301762 000018/2024</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>9452477</t>
+          <t>9454417</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>DM-9452477/2025</t>
+          <t>DM-9454417/2025</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F666" t="n">
@@ -37675,13 +37675,13 @@
         <v>1</v>
       </c>
       <c r="L666" t="n">
-        <v>52446095.99</v>
+        <v>38329183.15</v>
       </c>
       <c r="M666" t="n">
-        <v>52446095.99</v>
+        <v>38329183.15</v>
       </c>
       <c r="N666" t="n">
-        <v>39334571.99</v>
+        <v>28746887.36</v>
       </c>
     </row>
     <row r="667">
@@ -37690,22 +37690,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>2301762 000020/2024</t>
+          <t>2301762 000019/2024</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>9459013</t>
+          <t>9452477</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>DM-9459013/2025</t>
+          <t>DM-9452477/2025</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F667" t="n">
@@ -37731,13 +37731,13 @@
         <v>1</v>
       </c>
       <c r="L667" t="n">
-        <v>59309539.93</v>
+        <v>52446095.99</v>
       </c>
       <c r="M667" t="n">
-        <v>59309539.93</v>
+        <v>52446095.99</v>
       </c>
       <c r="N667" t="n">
-        <v>44482154.94</v>
+        <v>39334571.99</v>
       </c>
     </row>
     <row r="668">
@@ -37746,22 +37746,22 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>2301762 000021/2024</t>
+          <t>2301762 000020/2024</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>9453530</t>
+          <t>9459013</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>DM-9453530</t>
+          <t>DM-9459013/2025</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -37787,13 +37787,13 @@
         <v>1</v>
       </c>
       <c r="L668" t="n">
-        <v>9479564.210000001</v>
+        <v>59309539.93</v>
       </c>
       <c r="M668" t="n">
-        <v>9479564.210000001</v>
+        <v>59309539.93</v>
       </c>
       <c r="N668" t="n">
-        <v>7109673.15</v>
+        <v>44482154.94</v>
       </c>
     </row>
     <row r="669">
@@ -37802,22 +37802,22 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>2301762 000024/2025</t>
+          <t>2301762 000021/2024</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>9492723</t>
+          <t>9453530</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>DM-9492723/2025</t>
+          <t>DM-9453530</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F669" t="n">
@@ -37843,13 +37843,13 @@
         <v>1</v>
       </c>
       <c r="L669" t="n">
-        <v>60200606.24</v>
+        <v>9479564.210000001</v>
       </c>
       <c r="M669" t="n">
-        <v>60200606.24</v>
+        <v>9479564.210000001</v>
       </c>
       <c r="N669" t="n">
-        <v>41984578.11</v>
+        <v>7109673.15</v>
       </c>
     </row>
     <row r="670">
@@ -37858,54 +37858,54 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000024/2025</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9492723</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DM-9492723/2025</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>RAUTAKI TECNOLOGIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F670" t="n">
         <v>1</v>
       </c>
       <c r="G670" t="n">
-        <v>11207</v>
+        <v>1872</v>
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I670" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K670" t="n">
         <v>1</v>
       </c>
       <c r="L670" t="n">
-        <v>25269915.6</v>
+        <v>60200606.24</v>
       </c>
       <c r="M670" t="n">
-        <v>25269915.6</v>
+        <v>60200606.24</v>
       </c>
       <c r="N670" t="n">
-        <v>23434999.8</v>
+        <v>41984578.11</v>
       </c>
     </row>
     <row r="671">
@@ -37919,49 +37919,49 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>DO009482014/2025</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>RAUTAKI TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="F671" t="n">
         <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>66419</v>
+        <v>11207</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I671" t="n">
-        <v>3971</v>
+        <v>3951</v>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K671" t="n">
         <v>1</v>
       </c>
       <c r="L671" t="n">
-        <v>87218202.05</v>
+        <v>25269915.6</v>
       </c>
       <c r="M671" t="n">
-        <v>87218202.05</v>
+        <v>25269915.6</v>
       </c>
       <c r="N671" t="n">
-        <v>77898894.3</v>
+        <v>23434999.8</v>
       </c>
     </row>
     <row r="672">
@@ -37980,7 +37980,7 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DO009482014/2025</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -38031,17 +38031,17 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="F673" t="n">
@@ -38067,13 +38067,13 @@
         <v>1</v>
       </c>
       <c r="L673" t="n">
-        <v>79690903.56</v>
+        <v>87218202.05</v>
       </c>
       <c r="M673" t="n">
-        <v>79690903.56</v>
+        <v>87218202.05</v>
       </c>
       <c r="N673" t="n">
-        <v>47349998.43</v>
+        <v>77898894.3</v>
       </c>
     </row>
     <row r="674">
@@ -38087,17 +38087,17 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>TALENTECH - TECNOLOGIA LTDA</t>
+          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
         </is>
       </c>
       <c r="F674" t="n">
@@ -38123,13 +38123,13 @@
         <v>1</v>
       </c>
       <c r="L674" t="n">
-        <v>73884529.66</v>
+        <v>79690903.56</v>
       </c>
       <c r="M674" t="n">
-        <v>73884529.66</v>
+        <v>79690903.56</v>
       </c>
       <c r="N674" t="n">
-        <v>35989998.13</v>
+        <v>47349998.43</v>
       </c>
     </row>
     <row r="675">
@@ -38143,17 +38143,17 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>ELISEU KOPP &amp; CIA LTDA</t>
+          <t>TALENTECH - TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -38179,13 +38179,13 @@
         <v>1</v>
       </c>
       <c r="L675" t="n">
-        <v>75334510.38</v>
+        <v>73884529.66</v>
       </c>
       <c r="M675" t="n">
-        <v>75334510.38</v>
+        <v>73884529.66</v>
       </c>
       <c r="N675" t="n">
-        <v>45188997.86</v>
+        <v>35989998.13</v>
       </c>
     </row>
     <row r="676">
@@ -38199,17 +38199,17 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-009482032/2025-L6</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>DATA TRAFFIC S/A</t>
+          <t>TALENTECH - TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="F676" t="n">
@@ -38235,13 +38235,13 @@
         <v>1</v>
       </c>
       <c r="L676" t="n">
-        <v>65055206.84</v>
+        <v>73884529.66</v>
       </c>
       <c r="M676" t="n">
-        <v>65055206.84</v>
+        <v>73884529.66</v>
       </c>
       <c r="N676" t="n">
-        <v>32097999.96</v>
+        <v>35989998.13</v>
       </c>
     </row>
     <row r="677">
@@ -38250,54 +38250,54 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>9468567</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>AEST-9468567/2025</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>ELISEU KOPP &amp; CIA LTDA</t>
         </is>
       </c>
       <c r="F677" t="n">
         <v>1</v>
       </c>
       <c r="G677" t="n">
-        <v>26883</v>
+        <v>66419</v>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
         </is>
       </c>
       <c r="I677" t="n">
-        <v>3502</v>
+        <v>3971</v>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
         </is>
       </c>
       <c r="K677" t="n">
         <v>1</v>
       </c>
       <c r="L677" t="n">
-        <v>12267717.16</v>
+        <v>75334510.38</v>
       </c>
       <c r="M677" t="n">
-        <v>12267717.16</v>
+        <v>75334510.38</v>
       </c>
       <c r="N677" t="n">
-        <v>9200787.869999999</v>
+        <v>45188997.86</v>
       </c>
     </row>
     <row r="678">
@@ -38306,54 +38306,54 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>9468573</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>AEST-9468573/2025</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>DATA TRAFFIC S/A</t>
         </is>
       </c>
       <c r="F678" t="n">
         <v>1</v>
       </c>
       <c r="G678" t="n">
-        <v>26883</v>
+        <v>66419</v>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
+          <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
         </is>
       </c>
       <c r="I678" t="n">
-        <v>3502</v>
+        <v>3971</v>
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
+          <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
         </is>
       </c>
       <c r="K678" t="n">
         <v>1</v>
       </c>
       <c r="L678" t="n">
-        <v>12291296.66</v>
+        <v>65055206.84</v>
       </c>
       <c r="M678" t="n">
-        <v>12291296.66</v>
+        <v>65055206.84</v>
       </c>
       <c r="N678" t="n">
-        <v>9218472.49</v>
+        <v>32097999.96</v>
       </c>
     </row>
     <row r="679">
@@ -38367,17 +38367,17 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>9468704</t>
+          <t>9468567</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>AEST-9468704/2025</t>
+          <t>AEST-9468567/2025</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F679" t="n">
@@ -38403,13 +38403,13 @@
         <v>1</v>
       </c>
       <c r="L679" t="n">
-        <v>12197245.67</v>
+        <v>12267717.16</v>
       </c>
       <c r="M679" t="n">
-        <v>12197245.67</v>
+        <v>12267717.16</v>
       </c>
       <c r="N679" t="n">
-        <v>9147934.25</v>
+        <v>9200787.869999999</v>
       </c>
     </row>
     <row r="680">
@@ -38423,17 +38423,17 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>9469794</t>
+          <t>9468573</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AEST-9469794/2025</t>
+          <t>AEST-9468573/2025</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F680" t="n">
@@ -38459,13 +38459,13 @@
         <v>1</v>
       </c>
       <c r="L680" t="n">
-        <v>12379211.81</v>
+        <v>12291296.66</v>
       </c>
       <c r="M680" t="n">
-        <v>12379211.81</v>
+        <v>12291296.66</v>
       </c>
       <c r="N680" t="n">
-        <v>9284408.859999999</v>
+        <v>9218472.49</v>
       </c>
     </row>
     <row r="681">
@@ -38479,17 +38479,17 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>9470136</t>
+          <t>9468704</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>AEST-9470136/2025</t>
+          <t>AEST-9468704/2025</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F681" t="n">
@@ -38515,125 +38515,125 @@
         <v>1</v>
       </c>
       <c r="L681" t="n">
-        <v>12547127.86</v>
+        <v>12197245.67</v>
       </c>
       <c r="M681" t="n">
-        <v>12547127.86</v>
+        <v>12197245.67</v>
       </c>
       <c r="N681" t="n">
-        <v>9410345.9</v>
+        <v>9147934.25</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9469794</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t xml:space="preserve"> AEST-9469794/2025</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>PROCEC ENGENHARIA S.A</t>
+          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="F682" t="n">
         <v>1</v>
       </c>
       <c r="G682" t="n">
-        <v>1740</v>
+        <v>26883</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I682" t="n">
-        <v>5107</v>
+        <v>3502</v>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K682" t="n">
         <v>1</v>
       </c>
       <c r="L682" t="n">
-        <v>5887057.98</v>
+        <v>12379211.81</v>
       </c>
       <c r="M682" t="n">
-        <v>5887057.98</v>
+        <v>12379211.81</v>
       </c>
       <c r="N682" t="n">
-        <v>5658828.94</v>
+        <v>9284408.859999999</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9470136</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>AEST-9470136/2025</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>OPACO ENGENHARIA LTDA</t>
+          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
         </is>
       </c>
       <c r="F683" t="n">
         <v>1</v>
       </c>
       <c r="G683" t="n">
-        <v>1740</v>
+        <v>26883</v>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA RODOVIARIA</t>
         </is>
       </c>
       <c r="I683" t="n">
-        <v>5107</v>
+        <v>3502</v>
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE CONSULTORIA - PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K683" t="n">
         <v>1</v>
       </c>
       <c r="L683" t="n">
-        <v>28204745.51</v>
+        <v>12547127.86</v>
       </c>
       <c r="M683" t="n">
-        <v>28204745.51</v>
+        <v>12547127.86</v>
       </c>
       <c r="N683" t="n">
-        <v>28204745.51</v>
+        <v>9410345.9</v>
       </c>
     </row>
     <row r="684">
@@ -38642,22 +38642,22 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
+          <t>PROCEC ENGENHARIA S.A</t>
         </is>
       </c>
       <c r="F684" t="n">
@@ -38683,13 +38683,13 @@
         <v>1</v>
       </c>
       <c r="L684" t="n">
-        <v>4383662.29</v>
+        <v>5887057.98</v>
       </c>
       <c r="M684" t="n">
-        <v>4383662.29</v>
+        <v>5887057.98</v>
       </c>
       <c r="N684" t="n">
-        <v>3700000</v>
+        <v>5658828.94</v>
       </c>
     </row>
     <row r="685">
@@ -38698,18 +38698,22 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>9511902</t>
-        </is>
-      </c>
-      <c r="D685" t="inlineStr"/>
+          <t>9507997</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>OPACO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F685" t="n">
@@ -38732,16 +38736,16 @@
         </is>
       </c>
       <c r="K685" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L685" t="n">
-        <v>19733859.27</v>
+        <v>28204745.51</v>
       </c>
       <c r="M685" t="n">
-        <v>19733859.26</v>
+        <v>28204745.51</v>
       </c>
       <c r="N685" t="n">
-        <v>16179998.72</v>
+        <v>28204745.51</v>
       </c>
     </row>
     <row r="686">
@@ -38750,18 +38754,22 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>9515457</t>
-        </is>
-      </c>
-      <c r="D686" t="inlineStr"/>
+          <t>9497471</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>DC-9497471/2026</t>
+        </is>
+      </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
         </is>
       </c>
       <c r="F686" t="n">
@@ -38784,16 +38792,16 @@
         </is>
       </c>
       <c r="K686" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L686" t="n">
-        <v>120767701.47</v>
+        <v>4383662.29</v>
       </c>
       <c r="M686" t="n">
-        <v>120767701.47</v>
+        <v>4383662.29</v>
       </c>
       <c r="N686" t="n">
-        <v>87996201.20999999</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="687">
@@ -38802,18 +38810,22 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>2301520 000007/2026</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>9518140</t>
-        </is>
-      </c>
-      <c r="D687" t="inlineStr"/>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SINARCO LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F687" t="n">
@@ -38836,16 +38848,16 @@
         </is>
       </c>
       <c r="K687" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L687" t="n">
-        <v>83862492.89</v>
+        <v>19733859.27</v>
       </c>
       <c r="M687" t="n">
-        <v>83862492.89</v>
+        <v>19733859.26</v>
       </c>
       <c r="N687" t="n">
-        <v>77916642.14</v>
+        <v>16179998.72</v>
       </c>
     </row>
     <row r="688">
@@ -38854,17 +38866,17 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>2301520 000010/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>9498942</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>DC-011R/2024</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
@@ -38892,16 +38904,16 @@
         </is>
       </c>
       <c r="K688" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L688" t="n">
-        <v>2962697.76</v>
+        <v>120767701.47</v>
       </c>
       <c r="M688" t="n">
-        <v>2962697.76</v>
+        <v>120767701.47</v>
       </c>
       <c r="N688" t="n">
-        <v>2962697.76</v>
+        <v>87996201.20999999</v>
       </c>
     </row>
     <row r="689">
@@ -38910,15 +38922,19 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>2301520 000011/2026</t>
+          <t>2301520 000007/2026</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>9518942</t>
-        </is>
-      </c>
-      <c r="D689" t="inlineStr"/>
+          <t>9518140</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>DC-9518140/2026</t>
+        </is>
+      </c>
       <c r="E689" t="inlineStr">
         <is>
           <t>CONSTRUTORA SINARCO LTDA</t>
@@ -38947,13 +38963,13 @@
         <v>1</v>
       </c>
       <c r="L689" t="n">
-        <v>83450845.04000001</v>
+        <v>83862492.89</v>
       </c>
       <c r="M689" t="n">
-        <v>83450845.04000001</v>
+        <v>83862492.89</v>
       </c>
       <c r="N689" t="n">
-        <v>61779996.11</v>
+        <v>77916642.14</v>
       </c>
     </row>
     <row r="690">
@@ -38962,18 +38978,22 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>2301520 000017/2026</t>
+          <t>2301520 000010/2026</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>9519017</t>
-        </is>
-      </c>
-      <c r="D690" t="inlineStr"/>
+          <t>9498942</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>DC-011R/2024</t>
+        </is>
+      </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>BT CONSTRUCOES LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F690" t="n">
@@ -38999,13 +39019,13 @@
         <v>1</v>
       </c>
       <c r="L690" t="n">
-        <v>6602550.32</v>
+        <v>2962697.76</v>
       </c>
       <c r="M690" t="n">
-        <v>6602550.32</v>
+        <v>2962697.76</v>
       </c>
       <c r="N690" t="n">
-        <v>5995000</v>
+        <v>2962697.76</v>
       </c>
     </row>
     <row r="691">
@@ -39014,18 +39034,22 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>2301520 000023/2026</t>
+          <t>2301520 000011/2026</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>9519295</t>
-        </is>
-      </c>
-      <c r="D691" t="inlineStr"/>
+          <t>9518942</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>DC-9518942/2026</t>
+        </is>
+      </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>CONSTRUTORA SINARCO LTDA</t>
         </is>
       </c>
       <c r="F691" t="n">
@@ -39051,13 +39075,13 @@
         <v>1</v>
       </c>
       <c r="L691" t="n">
-        <v>37610115.71</v>
+        <v>83450845.04000001</v>
       </c>
       <c r="M691" t="n">
-        <v>37610115.71</v>
+        <v>83450845.04000001</v>
       </c>
       <c r="N691" t="n">
-        <v>34487308.95</v>
+        <v>61779996.11</v>
       </c>
     </row>
     <row r="692">
@@ -39066,18 +39090,22 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>2301520 000027/2026</t>
+          <t>2301520 000017/2026</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>9519020</t>
-        </is>
-      </c>
-      <c r="D692" t="inlineStr"/>
+          <t>9519017</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>DC-9519017/2026</t>
+        </is>
+      </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
+          <t>BT CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F692" t="n">
@@ -39103,13 +39131,13 @@
         <v>1</v>
       </c>
       <c r="L692" t="n">
-        <v>8481152.01</v>
+        <v>6602550.32</v>
       </c>
       <c r="M692" t="n">
-        <v>8481152.01</v>
+        <v>6602550.32</v>
       </c>
       <c r="N692" t="n">
-        <v>7088404.99</v>
+        <v>5995000</v>
       </c>
     </row>
     <row r="693">
@@ -39118,22 +39146,22 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>2301520 000030/2025</t>
+          <t>2301520 000023/2026</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>9495596</t>
+          <t>9519295</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>DC-9495596/2026</t>
+          <t>DC-9519295/2026</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F693" t="n">
@@ -39159,13 +39187,13 @@
         <v>1</v>
       </c>
       <c r="L693" t="n">
-        <v>15970367.44</v>
+        <v>37610115.71</v>
       </c>
       <c r="M693" t="n">
-        <v>15970367.44</v>
+        <v>37610115.71</v>
       </c>
       <c r="N693" t="n">
-        <v>12246077.75</v>
+        <v>34487308.95</v>
       </c>
     </row>
     <row r="694">
@@ -39174,54 +39202,54 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>2301520 000034/2025</t>
+          <t>2301520 000027/2026</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>9493122</t>
+          <t>9519020</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>DC-9493122/2026</t>
+          <t>DC-9519020/2026</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="F694" t="n">
         <v>1</v>
       </c>
       <c r="G694" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I694" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K694" t="n">
         <v>1</v>
       </c>
       <c r="L694" t="n">
-        <v>7420078.73</v>
+        <v>8481152.01</v>
       </c>
       <c r="M694" t="n">
-        <v>7420078.73</v>
+        <v>8481152.01</v>
       </c>
       <c r="N694" t="n">
-        <v>6677404.33</v>
+        <v>7088404.99</v>
       </c>
     </row>
     <row r="695">
@@ -39230,54 +39258,54 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>2301520 000035/2025</t>
+          <t>2301520 000030/2025</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>9492715</t>
+          <t>9495596</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>DC-9492715/2025</t>
+          <t>DC-9495596/2026</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F695" t="n">
         <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I695" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K695" t="n">
         <v>1</v>
       </c>
       <c r="L695" t="n">
-        <v>3563439</v>
+        <v>15970367.44</v>
       </c>
       <c r="M695" t="n">
-        <v>3563439</v>
+        <v>15970367.44</v>
       </c>
       <c r="N695" t="n">
-        <v>3028048.96</v>
+        <v>12246077.75</v>
       </c>
     </row>
     <row r="696">
@@ -39286,54 +39314,54 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301520 000034/2025</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9493122</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DC-9493122/2026</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CONTORNO LTDA</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F696" t="n">
         <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I696" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K696" t="n">
         <v>1</v>
       </c>
       <c r="L696" t="n">
-        <v>44004328.59</v>
+        <v>7420078.73</v>
       </c>
       <c r="M696" t="n">
-        <v>44004328.59</v>
+        <v>7420078.73</v>
       </c>
       <c r="N696" t="n">
-        <v>37600000</v>
+        <v>6677404.33</v>
       </c>
     </row>
     <row r="697">
@@ -39342,54 +39370,54 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301520 000035/2025</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9492715</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9492715/2025</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F697" t="n">
         <v>1</v>
       </c>
       <c r="G697" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I697" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K697" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L697" t="n">
-        <v>11144418.23</v>
+        <v>3563439</v>
       </c>
       <c r="M697" t="n">
-        <v>11144418.22</v>
+        <v>3563439</v>
       </c>
       <c r="N697" t="n">
-        <v>9814000</v>
+        <v>3028048.96</v>
       </c>
     </row>
     <row r="698">
@@ -39398,50 +39426,54 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>9498666</t>
-        </is>
-      </c>
-      <c r="D698" t="inlineStr"/>
+          <t>9493529</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>DC-9493529/2026</t>
+        </is>
+      </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>DYNATEST ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA CONTORNO LTDA</t>
         </is>
       </c>
       <c r="F698" t="n">
         <v>1</v>
       </c>
       <c r="G698" t="n">
-        <v>11207</v>
+        <v>1740</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I698" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K698" t="n">
         <v>1</v>
       </c>
       <c r="L698" t="n">
-        <v>32765091.84</v>
+        <v>44004328.59</v>
       </c>
       <c r="M698" t="n">
-        <v>32765091.84</v>
+        <v>44004328.59</v>
       </c>
       <c r="N698" t="n">
-        <v>23052682.68</v>
+        <v>37600000</v>
       </c>
     </row>
     <row r="699">
@@ -39450,50 +39482,54 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>2301520 000042/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>9501894</t>
-        </is>
-      </c>
-      <c r="D699" t="inlineStr"/>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F699" t="n">
         <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>10774</v>
+        <v>1740</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I699" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K699" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L699" t="n">
-        <v>6323844.01</v>
+        <v>11144418.23</v>
       </c>
       <c r="M699" t="n">
-        <v>6323844.01</v>
+        <v>11144418.22</v>
       </c>
       <c r="N699" t="n">
-        <v>4742883</v>
+        <v>9814000</v>
       </c>
     </row>
     <row r="700">
@@ -39502,54 +39538,50 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>9505062</t>
-        </is>
-      </c>
-      <c r="D700" t="inlineStr">
-        <is>
-          <t>DC-9505062/2026</t>
-        </is>
-      </c>
+          <t>9498666</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr">
         <is>
-          <t>S3 CONSTRUTORA LTDA - ME</t>
+          <t>DYNATEST ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F700" t="n">
         <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>1740</v>
+        <v>11207</v>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>SERVICOS DE SUPERVISAO DE OBRAS E SERVICOS DO SISTEMA VIARIO</t>
         </is>
       </c>
       <c r="I700" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K700" t="n">
         <v>1</v>
       </c>
       <c r="L700" t="n">
-        <v>3965005.14</v>
+        <v>32765091.84</v>
       </c>
       <c r="M700" t="n">
-        <v>3965005.14</v>
+        <v>32765091.84</v>
       </c>
       <c r="N700" t="n">
-        <v>2961858.83</v>
+        <v>23052682.68</v>
       </c>
     </row>
     <row r="701">
@@ -39558,50 +39590,54 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>2301520 000042/2025</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>9518766</t>
-        </is>
-      </c>
-      <c r="D701" t="inlineStr"/>
+          <t>9501894</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>DC-9501894/2026</t>
+        </is>
+      </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>MAIS CONSTRUTORA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F701" t="n">
         <v>1</v>
       </c>
       <c r="G701" t="n">
-        <v>1740</v>
+        <v>10774</v>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
+          <t>ESTUDOS E PROJETOS NA AREA DE ENGENHARIA RODOVIARIA, AEROVIARIA ETC</t>
         </is>
       </c>
       <c r="I701" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K701" t="n">
         <v>1</v>
       </c>
       <c r="L701" t="n">
-        <v>151298828.22</v>
+        <v>6323844.01</v>
       </c>
       <c r="M701" t="n">
-        <v>151298828.22</v>
+        <v>6323844.01</v>
       </c>
       <c r="N701" t="n">
-        <v>120800000</v>
+        <v>4742883</v>
       </c>
     </row>
     <row r="702">
@@ -39610,54 +39646,54 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>STE SERVICOS TECNICOS DE ENGENHARIA SA</t>
+          <t>S3 CONSTRUTORA LTDA - ME</t>
         </is>
       </c>
       <c r="F702" t="n">
         <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>115827</v>
+        <v>1740</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICOS TECNICOS EM AREA AMBIENTAL </t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I702" t="n">
-        <v>3973</v>
+        <v>5107</v>
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K702" t="n">
         <v>1</v>
       </c>
       <c r="L702" t="n">
-        <v>48044257.29</v>
+        <v>3965005.14</v>
       </c>
       <c r="M702" t="n">
-        <v>48044257.29</v>
+        <v>3965005.14</v>
       </c>
       <c r="N702" t="n">
-        <v>36033198.22</v>
+        <v>2961858.83</v>
       </c>
     </row>
     <row r="703">
@@ -39666,54 +39702,54 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2301617 000004/2025</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>9502187</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
+          <t>MAIS CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="F703" t="n">
         <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>23167</v>
+        <v>1740</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I703" t="n">
-        <v>3999</v>
+        <v>5107</v>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K703" t="n">
         <v>1</v>
       </c>
       <c r="L703" t="n">
-        <v>1904028.2</v>
+        <v>151298828.22</v>
       </c>
       <c r="M703" t="n">
-        <v>1904028.2</v>
+        <v>151298828.22</v>
       </c>
       <c r="N703" t="n">
-        <v>1768342.65</v>
+        <v>120800000</v>
       </c>
     </row>
     <row r="704">
@@ -39722,54 +39758,54 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>9493180</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>DM-9493180/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>STE SERVICOS TECNICOS DE ENGENHARIA SA</t>
         </is>
       </c>
       <c r="F704" t="n">
         <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>1872</v>
+        <v>115827</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t xml:space="preserve">SERVICOS TECNICOS EM AREA AMBIENTAL </t>
         </is>
       </c>
       <c r="I704" t="n">
-        <v>5107</v>
+        <v>3973</v>
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICO DE ENGENHARIA PARA OPERACAO DE BENS DE DOMINIO PUBLICO</t>
         </is>
       </c>
       <c r="K704" t="n">
         <v>1</v>
       </c>
       <c r="L704" t="n">
-        <v>99982008.22</v>
+        <v>48044257.29</v>
       </c>
       <c r="M704" t="n">
-        <v>99982008.22</v>
+        <v>48044257.29</v>
       </c>
       <c r="N704" t="n">
-        <v>64984305.34</v>
+        <v>36033198.22</v>
       </c>
     </row>
     <row r="705">
@@ -39778,50 +39814,54 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>2301762 000001/2026</t>
+          <t>2301617 000004/2025</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>9512044</t>
-        </is>
-      </c>
-      <c r="D705" t="inlineStr"/>
+          <t>9502187</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>E+ ENGENHARIA E MEIO AMBIENTE LTDA</t>
         </is>
       </c>
       <c r="F705" t="n">
         <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>1872</v>
+        <v>23167</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS TECNICOS  ESPECIALIZADOS  EM ELABORACAO DE PROJETOSEXECUTIVOS</t>
         </is>
       </c>
       <c r="I705" t="n">
-        <v>5107</v>
+        <v>3999</v>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>OUTROS SERVICOS PESSOA JURIDICA</t>
         </is>
       </c>
       <c r="K705" t="n">
         <v>1</v>
       </c>
       <c r="L705" t="n">
-        <v>13602005.38</v>
+        <v>1904028.2</v>
       </c>
       <c r="M705" t="n">
-        <v>13602005.38</v>
+        <v>1904028.2</v>
       </c>
       <c r="N705" t="n">
-        <v>11358610.11</v>
+        <v>1768342.65</v>
       </c>
     </row>
     <row r="706">
@@ -39830,18 +39870,22 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>2301762 000004/2026</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>9512043</t>
-        </is>
-      </c>
-      <c r="D706" t="inlineStr"/>
+          <t>9493180</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>DM-9493180/2026</t>
+        </is>
+      </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="F706" t="n">
@@ -39867,13 +39911,13 @@
         <v>1</v>
       </c>
       <c r="L706" t="n">
-        <v>73340224.20999999</v>
+        <v>99982008.22</v>
       </c>
       <c r="M706" t="n">
-        <v>73340224.20999999</v>
+        <v>99982008.22</v>
       </c>
       <c r="N706" t="n">
-        <v>44002130</v>
+        <v>64984305.34</v>
       </c>
     </row>
     <row r="707">
@@ -39882,22 +39926,22 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>2301762 000022/2025</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>9493137</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>DM-9493137/2026</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>CONSTRUTORA ITAMARACA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F707" t="n">
@@ -39923,13 +39967,13 @@
         <v>1</v>
       </c>
       <c r="L707" t="n">
-        <v>11437822.96</v>
+        <v>13602005.38</v>
       </c>
       <c r="M707" t="n">
-        <v>11437822.96</v>
+        <v>13602005.38</v>
       </c>
       <c r="N707" t="n">
-        <v>10619818.83</v>
+        <v>11358610.11</v>
       </c>
     </row>
     <row r="708">
@@ -39938,22 +39982,22 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F708" t="n">
@@ -39979,13 +40023,13 @@
         <v>1</v>
       </c>
       <c r="L708" t="n">
-        <v>19019690.63</v>
+        <v>73340224.20999999</v>
       </c>
       <c r="M708" t="n">
-        <v>19019690.63</v>
+        <v>73340224.20999999</v>
       </c>
       <c r="N708" t="n">
-        <v>14264750.82</v>
+        <v>44002130</v>
       </c>
     </row>
     <row r="709">
@@ -39994,22 +40038,22 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>2301762 000025/2025</t>
+          <t>2301762 000022/2025</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>9493202</t>
+          <t>9493137</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>DM-9493202/2026</t>
+          <t>DM-9493137/2026</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>CONSTRUTORA ITAMARACA LTDA</t>
         </is>
       </c>
       <c r="F709" t="n">
@@ -40035,13 +40079,13 @@
         <v>1</v>
       </c>
       <c r="L709" t="n">
-        <v>6305546.68</v>
+        <v>11437822.96</v>
       </c>
       <c r="M709" t="n">
-        <v>6305546.68</v>
+        <v>11437822.96</v>
       </c>
       <c r="N709" t="n">
-        <v>4557819.64</v>
+        <v>10619818.83</v>
       </c>
     </row>
     <row r="710">
@@ -40050,54 +40094,54 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F710" t="n">
         <v>1</v>
       </c>
       <c r="G710" t="n">
-        <v>8125</v>
+        <v>1872</v>
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I710" t="n">
-        <v>3951</v>
+        <v>5107</v>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K710" t="n">
         <v>1</v>
       </c>
       <c r="L710" t="n">
-        <v>8281446.48</v>
+        <v>19019690.63</v>
       </c>
       <c r="M710" t="n">
-        <v>0</v>
+        <v>19019690.63</v>
       </c>
       <c r="N710" t="n">
-        <v>0</v>
+        <v>14264750.82</v>
       </c>
     </row>
     <row r="711">
@@ -40106,54 +40150,54 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000025/2025</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9493202</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-9493202/2026</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F711" t="n">
         <v>1</v>
       </c>
       <c r="G711" t="n">
-        <v>8125</v>
+        <v>1872</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I711" t="n">
-        <v>5106</v>
+        <v>5107</v>
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K711" t="n">
         <v>1</v>
       </c>
       <c r="L711" t="n">
-        <v>8281446.48</v>
+        <v>6305546.68</v>
       </c>
       <c r="M711" t="n">
-        <v>8281446.48</v>
+        <v>6305546.68</v>
       </c>
       <c r="N711" t="n">
-        <v>5342582.88</v>
+        <v>4557819.64</v>
       </c>
     </row>
     <row r="712">
@@ -40162,50 +40206,54 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>9500304</t>
-        </is>
-      </c>
-      <c r="D712" t="inlineStr"/>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F712" t="n">
         <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>1872</v>
+        <v>8125</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
         </is>
       </c>
       <c r="I712" t="n">
-        <v>5107</v>
+        <v>3951</v>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICOS DE GERENCIAMENTO, SUPERVISAO E FISCALIZACAO DE OBRAS</t>
         </is>
       </c>
       <c r="K712" t="n">
         <v>1</v>
       </c>
       <c r="L712" t="n">
-        <v>16936267.4</v>
+        <v>8281446.48</v>
       </c>
       <c r="M712" t="n">
-        <v>16936267.4</v>
+        <v>0</v>
       </c>
       <c r="N712" t="n">
-        <v>14124998.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="713">
@@ -40214,50 +40262,54 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>2301762 000028/2025</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>9519034</t>
-        </is>
-      </c>
-      <c r="D713" t="inlineStr"/>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F713" t="n">
         <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>1872</v>
+        <v>8125</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE CONSULTORIA EM AREA DE ENGENHARIA CIVIL</t>
         </is>
       </c>
       <c r="I713" t="n">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>ESTUDOS E PROJETOS DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K713" t="n">
         <v>1</v>
       </c>
       <c r="L713" t="n">
-        <v>64979801.54</v>
+        <v>8281446.48</v>
       </c>
       <c r="M713" t="n">
-        <v>64979801.54</v>
+        <v>8281446.48</v>
       </c>
       <c r="N713" t="n">
-        <v>46640000</v>
+        <v>5342582.88</v>
       </c>
     </row>
     <row r="714">
@@ -40266,22 +40318,22 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPRESA DE CONSERVACAO BRASILEIRA LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F714" t="n">
@@ -40307,13 +40359,13 @@
         <v>1</v>
       </c>
       <c r="L714" t="n">
-        <v>28640371.76</v>
+        <v>16936267.4</v>
       </c>
       <c r="M714" t="n">
-        <v>28640371.76</v>
+        <v>16936267.4</v>
       </c>
       <c r="N714" t="n">
-        <v>19798000</v>
+        <v>14124998.39</v>
       </c>
     </row>
     <row r="715">
@@ -40322,161 +40374,173 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
+          <t>2301762 000028/2025</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>DM-9519034/2026</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="F715" t="n">
+        <v>1</v>
+      </c>
+      <c r="G715" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I715" t="n">
+        <v>5107</v>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="K715" t="n">
+        <v>1</v>
+      </c>
+      <c r="L715" t="n">
+        <v>64979801.54</v>
+      </c>
+      <c r="M715" t="n">
+        <v>64979801.54</v>
+      </c>
+      <c r="N715" t="n">
+        <v>46640000</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>2301762 000030/2025</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>9504058</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>DM-9504058/2026</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>EMCONBRAS EMPRESA DE CONSERVACAO BRASILEIRA LTDA</t>
+        </is>
+      </c>
+      <c r="F716" t="n">
+        <v>1</v>
+      </c>
+      <c r="G716" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I716" t="n">
+        <v>5107</v>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="K716" t="n">
+        <v>1</v>
+      </c>
+      <c r="L716" t="n">
+        <v>28640371.76</v>
+      </c>
+      <c r="M716" t="n">
+        <v>28640371.76</v>
+      </c>
+      <c r="N716" t="n">
+        <v>19798000</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
           <t>2301901 000001/2025</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr">
+      <c r="C717" t="inlineStr">
         <is>
           <t>9493205</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr">
+      <c r="D717" t="inlineStr">
         <is>
           <t>DO-9493205/2026-L4</t>
         </is>
       </c>
-      <c r="E715" t="inlineStr">
+      <c r="E717" t="inlineStr">
         <is>
           <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
         </is>
       </c>
-      <c r="F715" t="n">
-        <v>1</v>
-      </c>
-      <c r="G715" t="n">
+      <c r="F717" t="n">
+        <v>1</v>
+      </c>
+      <c r="G717" t="n">
         <v>66419</v>
       </c>
-      <c r="H715" t="inlineStr">
+      <c r="H717" t="inlineStr">
         <is>
           <t>SERVICO DE VIGILANCIA ELETRONICA DE TRANSITO E TRAFEGO E    TRATAMENTO DAS IMAGENS</t>
         </is>
       </c>
-      <c r="I715" t="n">
+      <c r="I717" t="n">
         <v>3971</v>
       </c>
-      <c r="J715" t="inlineStr">
+      <c r="J717" t="inlineStr">
         <is>
           <t>SERVICOS TECN DE IMPLANTACAO GESTAO E ADM DO SIST DE OBSERV ELETRONICA</t>
         </is>
       </c>
-      <c r="K715" t="n">
-        <v>1</v>
-      </c>
-      <c r="L715" t="n">
+      <c r="K717" t="n">
+        <v>1</v>
+      </c>
+      <c r="L717" t="n">
         <v>64031795.21</v>
       </c>
-      <c r="M715" t="n">
+      <c r="M717" t="n">
         <v>64031795.21</v>
       </c>
-      <c r="N715" t="n">
+      <c r="N717" t="n">
         <v>31699998.96</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr"/>
-      <c r="B716" t="inlineStr">
-        <is>
-          <t>2301520 000001/2020</t>
-        </is>
-      </c>
-      <c r="C716" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D716" t="inlineStr"/>
-      <c r="E716" t="inlineStr">
-        <is>
-          <t>INEXISTENTE</t>
-        </is>
-      </c>
-      <c r="F716" t="n">
-        <v>1</v>
-      </c>
-      <c r="G716" t="n">
-        <v>1740</v>
-      </c>
-      <c r="H716" t="inlineStr">
-        <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
-        </is>
-      </c>
-      <c r="I716" t="n">
-        <v>5107</v>
-      </c>
-      <c r="J716" t="inlineStr">
-        <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
-        </is>
-      </c>
-      <c r="K716" t="n">
-        <v>1</v>
-      </c>
-      <c r="L716" t="n">
-        <v>4668587.23</v>
-      </c>
-      <c r="M716" t="n">
-        <v>0</v>
-      </c>
-      <c r="N716" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr"/>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>2301520 000001/2021</t>
-        </is>
-      </c>
-      <c r="C717" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr">
-        <is>
-          <t>IPE ENGENHARIA LTDA</t>
-        </is>
-      </c>
-      <c r="F717" t="n">
-        <v>1</v>
-      </c>
-      <c r="G717" t="n">
-        <v>1740</v>
-      </c>
-      <c r="H717" t="inlineStr">
-        <is>
-          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
-        </is>
-      </c>
-      <c r="I717" t="n">
-        <v>5107</v>
-      </c>
-      <c r="J717" t="inlineStr">
-        <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
-        </is>
-      </c>
-      <c r="K717" t="n">
-        <v>1</v>
-      </c>
-      <c r="L717" t="n">
-        <v>16217686.32</v>
-      </c>
-      <c r="M717" t="n">
-        <v>16217686.32</v>
-      </c>
-      <c r="N717" t="n">
-        <v>12796116.03</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr"/>
       <c r="B718" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301520 000001/2020</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -40510,10 +40574,10 @@
         </is>
       </c>
       <c r="K718" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L718" t="n">
-        <v>18465630.31</v>
+        <v>4668587.23</v>
       </c>
       <c r="M718" t="n">
         <v>0</v>
@@ -40526,7 +40590,7 @@
       <c r="A719" t="inlineStr"/>
       <c r="B719" t="inlineStr">
         <is>
-          <t>2301520 000006/2020</t>
+          <t>2301520 000001/2021</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -40537,18 +40601,18 @@
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F719" t="n">
         <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>1872</v>
+        <v>1740</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I719" t="n">
@@ -40563,20 +40627,20 @@
         <v>1</v>
       </c>
       <c r="L719" t="n">
-        <v>46371045.53</v>
+        <v>16217686.32</v>
       </c>
       <c r="M719" t="n">
-        <v>46371045.53</v>
+        <v>16217686.32</v>
       </c>
       <c r="N719" t="n">
-        <v>34303736.06</v>
+        <v>12796116.03</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr"/>
       <c r="B720" t="inlineStr">
         <is>
-          <t>2301520 000013/2021</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -40587,7 +40651,7 @@
       <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr">
         <is>
-          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F720" t="n">
@@ -40610,23 +40674,23 @@
         </is>
       </c>
       <c r="K720" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L720" t="n">
-        <v>2022624.54</v>
+        <v>18465630.31</v>
       </c>
       <c r="M720" t="n">
-        <v>2022624.54</v>
+        <v>0</v>
       </c>
       <c r="N720" t="n">
-        <v>1704806.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr"/>
       <c r="B721" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301520 000006/2020</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -40637,46 +40701,46 @@
       <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F721" t="n">
         <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>108600</v>
+        <v>1872</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
         </is>
       </c>
       <c r="I721" t="n">
-        <v>3964</v>
+        <v>5107</v>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K721" t="n">
         <v>1</v>
       </c>
       <c r="L721" t="n">
-        <v>540000</v>
+        <v>46371045.53</v>
       </c>
       <c r="M721" t="n">
-        <v>540000</v>
+        <v>46371045.53</v>
       </c>
       <c r="N721" t="n">
-        <v>540000</v>
+        <v>34303736.06</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr"/>
       <c r="B722" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301520 000013/2021</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -40687,39 +40751,39 @@
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
         </is>
       </c>
       <c r="F722" t="n">
         <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>108600</v>
+        <v>1740</v>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
+          <t>SERVICOS DE IMPLANTACAO E PAVIMENTACAO ASFALTICA</t>
         </is>
       </c>
       <c r="I722" t="n">
-        <v>3964</v>
+        <v>5107</v>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
         </is>
       </c>
       <c r="K722" t="n">
         <v>1</v>
       </c>
       <c r="L722" t="n">
-        <v>454999.67</v>
+        <v>2022624.54</v>
       </c>
       <c r="M722" t="n">
-        <v>454999.67</v>
+        <v>2022624.54</v>
       </c>
       <c r="N722" t="n">
-        <v>454999.67</v>
+        <v>1704806.45</v>
       </c>
     </row>
     <row r="723">
@@ -40737,7 +40801,7 @@
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="F723" t="n">
@@ -40763,13 +40827,13 @@
         <v>1</v>
       </c>
       <c r="L723" t="n">
-        <v>508997.33</v>
+        <v>540000</v>
       </c>
       <c r="M723" t="n">
-        <v>508997.33</v>
+        <v>540000</v>
       </c>
       <c r="N723" t="n">
-        <v>508997.33</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="724">
@@ -40787,7 +40851,7 @@
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F724" t="n">
@@ -40813,13 +40877,13 @@
         <v>1</v>
       </c>
       <c r="L724" t="n">
-        <v>386990</v>
+        <v>454999.67</v>
       </c>
       <c r="M724" t="n">
-        <v>386990</v>
+        <v>454999.67</v>
       </c>
       <c r="N724" t="n">
-        <v>386990</v>
+        <v>454999.67</v>
       </c>
     </row>
     <row r="725">
@@ -40837,7 +40901,7 @@
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F725" t="n">
@@ -40863,13 +40927,13 @@
         <v>1</v>
       </c>
       <c r="L725" t="n">
-        <v>384900</v>
+        <v>508997.33</v>
       </c>
       <c r="M725" t="n">
-        <v>384900</v>
+        <v>508997.33</v>
       </c>
       <c r="N725" t="n">
-        <v>384900</v>
+        <v>508997.33</v>
       </c>
     </row>
     <row r="726">
@@ -40887,7 +40951,7 @@
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F726" t="n">
@@ -40913,20 +40977,20 @@
         <v>1</v>
       </c>
       <c r="L726" t="n">
-        <v>566000</v>
+        <v>386990</v>
       </c>
       <c r="M726" t="n">
-        <v>566000</v>
+        <v>386990</v>
       </c>
       <c r="N726" t="n">
-        <v>566000</v>
+        <v>386990</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr"/>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -40937,46 +41001,46 @@
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="F727" t="n">
         <v>1</v>
       </c>
       <c r="G727" t="n">
-        <v>23159</v>
+        <v>108600</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
         </is>
       </c>
       <c r="I727" t="n">
-        <v>3981</v>
+        <v>3964</v>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
         </is>
       </c>
       <c r="K727" t="n">
         <v>1</v>
       </c>
       <c r="L727" t="n">
-        <v>1947867.48</v>
+        <v>384900</v>
       </c>
       <c r="M727" t="n">
-        <v>0</v>
+        <v>384900</v>
       </c>
       <c r="N727" t="n">
-        <v>0</v>
+        <v>384900</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr"/>
       <c r="B728" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -40987,39 +41051,39 @@
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="F728" t="n">
         <v>1</v>
       </c>
       <c r="G728" t="n">
-        <v>23159</v>
+        <v>108600</v>
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
+          <t>SERVICOS DE TOPOGRAFICA COM LEVANTAMENTO TOPOGRAFICO PLANIALTIMETRICO E CADASTRAL</t>
         </is>
       </c>
       <c r="I728" t="n">
-        <v>3981</v>
+        <v>3964</v>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
+          <t>SERVICOS DE MAPEAMENTO E GEORREFERENCIAMENTO</t>
         </is>
       </c>
       <c r="K728" t="n">
         <v>1</v>
       </c>
       <c r="L728" t="n">
-        <v>2235628.88</v>
+        <v>566000</v>
       </c>
       <c r="M728" t="n">
-        <v>0</v>
+        <v>566000</v>
       </c>
       <c r="N728" t="n">
-        <v>0</v>
+        <v>566000</v>
       </c>
     </row>
     <row r="729">
@@ -41063,7 +41127,7 @@
         <v>1</v>
       </c>
       <c r="L729" t="n">
-        <v>2251859.48</v>
+        <v>1947867.48</v>
       </c>
       <c r="M729" t="n">
         <v>0</v>
@@ -41076,7 +41140,7 @@
       <c r="A730" t="inlineStr"/>
       <c r="B730" t="inlineStr">
         <is>
-          <t>2301762 000005/2023</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -41087,46 +41151,46 @@
       <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr">
         <is>
-          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F730" t="n">
         <v>1</v>
       </c>
       <c r="G730" t="n">
-        <v>1872</v>
+        <v>23159</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I730" t="n">
-        <v>5107</v>
+        <v>3981</v>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K730" t="n">
         <v>1</v>
       </c>
       <c r="L730" t="n">
-        <v>10768247.16</v>
+        <v>2235628.88</v>
       </c>
       <c r="M730" t="n">
-        <v>10768247.16</v>
+        <v>0</v>
       </c>
       <c r="N730" t="n">
-        <v>8795462.050000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr"/>
       <c r="B731" t="inlineStr">
         <is>
-          <t>2301762 000016/2017</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -41137,46 +41201,46 @@
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr">
         <is>
-          <t>DIEFRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>INEXISTENTE</t>
         </is>
       </c>
       <c r="F731" t="n">
         <v>1</v>
       </c>
       <c r="G731" t="n">
-        <v>1872</v>
+        <v>23159</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+          <t>SERVICOS ESPECIALIZADOS EM ESTUDO E SONDAGEM DE SOLOS</t>
         </is>
       </c>
       <c r="I731" t="n">
-        <v>5107</v>
+        <v>3981</v>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+          <t>SERVICO DE ELABORACAO DE ESTUDOS PREVIOS</t>
         </is>
       </c>
       <c r="K731" t="n">
         <v>1</v>
       </c>
       <c r="L731" t="n">
-        <v>24277046.87</v>
+        <v>2251859.48</v>
       </c>
       <c r="M731" t="n">
-        <v>24277046.87</v>
+        <v>0</v>
       </c>
       <c r="N731" t="n">
-        <v>24277046.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr"/>
       <c r="B732" t="inlineStr">
         <is>
-          <t>2301762 000016/2017</t>
+          <t>2301762 000005/2023</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -41187,7 +41251,7 @@
       <c r="D732" t="inlineStr"/>
       <c r="E732" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
         </is>
       </c>
       <c r="F732" t="n">
@@ -41213,12 +41277,112 @@
         <v>1</v>
       </c>
       <c r="L732" t="n">
+        <v>10768247.16</v>
+      </c>
+      <c r="M732" t="n">
+        <v>10768247.16</v>
+      </c>
+      <c r="N732" t="n">
+        <v>8795462.050000001</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr"/>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>2301762 000016/2017</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr"/>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>DIEFRA ENGENHARIA E CONSULTORIA LTDA</t>
+        </is>
+      </c>
+      <c r="F733" t="n">
+        <v>1</v>
+      </c>
+      <c r="G733" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I733" t="n">
+        <v>5107</v>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="K733" t="n">
+        <v>1</v>
+      </c>
+      <c r="L733" t="n">
+        <v>24277046.87</v>
+      </c>
+      <c r="M733" t="n">
+        <v>24277046.87</v>
+      </c>
+      <c r="N733" t="n">
+        <v>24277046.87</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr"/>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>2301762 000016/2017</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr"/>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+        </is>
+      </c>
+      <c r="F734" t="n">
+        <v>1</v>
+      </c>
+      <c r="G734" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>SERVICOS DE RECUPERACAO DE RODOVIAS</t>
+        </is>
+      </c>
+      <c r="I734" t="n">
+        <v>5107</v>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="K734" t="n">
+        <v>1</v>
+      </c>
+      <c r="L734" t="n">
         <v>12102613.88</v>
       </c>
-      <c r="M732" t="n">
+      <c r="M734" t="n">
         <v>12102613.88</v>
       </c>
-      <c r="N732" t="n">
+      <c r="N734" t="n">
         <v>12102613.88</v>
       </c>
     </row>
